--- a/research/traditional_assets/database/data/hungary/hungary_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/hungary/hungary_beverage_alcoholic.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09329378793608531</v>
+        <v>0.09325077352694283</v>
       </c>
       <c r="C2">
-        <v>126.4</v>
+        <v>125.2101020427946</v>
       </c>
       <c r="D2">
-        <v>122.85</v>
+        <v>122.9241020427946</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1.264</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.264</v>
       </c>
       <c r="G2">
         <v>3.55</v>
@@ -1451,28 +1451,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0635792</v>
       </c>
       <c r="N2">
-        <v>9.469999999999999</v>
+        <v>9.406420799999999</v>
       </c>
       <c r="O2">
-        <v>0.8522999999999998</v>
+        <v>0.8465778719999999</v>
       </c>
       <c r="P2">
-        <v>8.617699999999999</v>
+        <v>8.559842928</v>
       </c>
       <c r="Q2">
-        <v>10.3477</v>
+        <v>10.289842928</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09329378793608531</v>
+        <v>0.09373034699691195</v>
       </c>
       <c r="T2">
-        <v>0.6910924838905985</v>
+        <v>0.6974449501566636</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>148.9480836499987</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09325077352694283</v>
+        <v>0.09320775911780035</v>
       </c>
       <c r="C3">
-        <v>125.2101020427946</v>
+        <v>124.0202935349491</v>
       </c>
       <c r="D3">
-        <v>122.9241020427946</v>
+        <v>122.9982935349491</v>
       </c>
       <c r="E3">
-        <v>1.264</v>
+        <v>2.528</v>
       </c>
       <c r="F3">
-        <v>1.264</v>
+        <v>2.528</v>
       </c>
       <c r="G3">
         <v>3.55</v>
@@ -1533,28 +1533,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M3">
-        <v>0.0635792</v>
+        <v>0.1271584</v>
       </c>
       <c r="N3">
-        <v>9.406420799999999</v>
+        <v>9.342841599999998</v>
       </c>
       <c r="O3">
-        <v>0.8465778719999999</v>
+        <v>0.8408557439999998</v>
       </c>
       <c r="P3">
-        <v>8.559842928</v>
+        <v>8.501985855999997</v>
       </c>
       <c r="Q3">
-        <v>10.289842928</v>
+        <v>10.231985856</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09373034699691195</v>
+        <v>0.09417581542632689</v>
       </c>
       <c r="T3">
-        <v>0.6974449501566636</v>
+        <v>0.703927058591424</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>148.9480836499987</v>
+        <v>74.47404182499935</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09320775911780035</v>
+        <v>0.09316474470865788</v>
       </c>
       <c r="C4">
-        <v>124.0202935349491</v>
+        <v>122.8305746385243</v>
       </c>
       <c r="D4">
-        <v>122.9982935349491</v>
+        <v>123.0725746385243</v>
       </c>
       <c r="E4">
-        <v>2.528</v>
+        <v>3.792</v>
       </c>
       <c r="F4">
-        <v>2.528</v>
+        <v>3.792</v>
       </c>
       <c r="G4">
         <v>3.55</v>
@@ -1615,28 +1615,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M4">
-        <v>0.1271584</v>
+        <v>0.1907376</v>
       </c>
       <c r="N4">
-        <v>9.342841599999998</v>
+        <v>9.279262399999999</v>
       </c>
       <c r="O4">
-        <v>0.8408557439999998</v>
+        <v>0.8351336159999998</v>
       </c>
       <c r="P4">
-        <v>8.501985855999997</v>
+        <v>8.444128783999998</v>
       </c>
       <c r="Q4">
-        <v>10.231985856</v>
+        <v>10.174128784</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09417581542632689</v>
+        <v>0.09463046877181225</v>
       </c>
       <c r="T4">
-        <v>0.703927058591424</v>
+        <v>0.7105428187464886</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>74.47404182499935</v>
+        <v>49.64936121666624</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09316474470865788</v>
+        <v>0.0931217302995154</v>
       </c>
       <c r="C5">
-        <v>122.8305746385243</v>
+        <v>121.6409455159727</v>
       </c>
       <c r="D5">
-        <v>123.0725746385243</v>
+        <v>123.1469455159727</v>
       </c>
       <c r="E5">
-        <v>3.792</v>
+        <v>5.056</v>
       </c>
       <c r="F5">
-        <v>3.792</v>
+        <v>5.056</v>
       </c>
       <c r="G5">
         <v>3.55</v>
@@ -1697,28 +1697,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M5">
-        <v>0.1907376</v>
+        <v>0.2543168</v>
       </c>
       <c r="N5">
-        <v>9.279262399999999</v>
+        <v>9.215683199999999</v>
       </c>
       <c r="O5">
-        <v>0.8351336159999998</v>
+        <v>0.8294114879999999</v>
       </c>
       <c r="P5">
-        <v>8.444128783999998</v>
+        <v>8.386271711999999</v>
       </c>
       <c r="Q5">
-        <v>10.174128784</v>
+        <v>10.116271712</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09463046877181225</v>
+        <v>0.09509459406199521</v>
       </c>
       <c r="T5">
-        <v>0.7105428187464886</v>
+        <v>0.7172964072381171</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>49.64936121666624</v>
+        <v>37.23702091249968</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0931217302995154</v>
+        <v>0.09307871589037292</v>
       </c>
       <c r="C6">
-        <v>121.6409455159727</v>
+        <v>120.4514063301395</v>
       </c>
       <c r="D6">
-        <v>123.1469455159727</v>
+        <v>123.2214063301396</v>
       </c>
       <c r="E6">
-        <v>5.056</v>
+        <v>6.32</v>
       </c>
       <c r="F6">
-        <v>5.056</v>
+        <v>6.32</v>
       </c>
       <c r="G6">
         <v>3.55</v>
@@ -1779,28 +1779,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M6">
-        <v>0.2543168</v>
+        <v>0.317896</v>
       </c>
       <c r="N6">
-        <v>9.215683199999999</v>
+        <v>9.152104</v>
       </c>
       <c r="O6">
-        <v>0.8294114879999999</v>
+        <v>0.8236893599999999</v>
       </c>
       <c r="P6">
-        <v>8.386271711999999</v>
+        <v>8.32841464</v>
       </c>
       <c r="Q6">
-        <v>10.116271712</v>
+        <v>10.05841464</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09509459406199521</v>
+        <v>0.09556849041091886</v>
       </c>
       <c r="T6">
-        <v>0.7172964072381171</v>
+        <v>0.7241921765400956</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>37.23702091249968</v>
+        <v>29.78961672999975</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09307871589037292</v>
+        <v>0.09303570148123046</v>
       </c>
       <c r="C7">
-        <v>120.4514063301395</v>
+        <v>119.2619572442643</v>
       </c>
       <c r="D7">
-        <v>123.2214063301396</v>
+        <v>123.2959572442643</v>
       </c>
       <c r="E7">
-        <v>6.32</v>
+        <v>7.584000000000001</v>
       </c>
       <c r="F7">
-        <v>6.32</v>
+        <v>7.584000000000001</v>
       </c>
       <c r="G7">
         <v>3.55</v>
@@ -1861,28 +1861,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M7">
-        <v>0.317896</v>
+        <v>0.3814752</v>
       </c>
       <c r="N7">
-        <v>9.152104</v>
+        <v>9.088524799999998</v>
       </c>
       <c r="O7">
-        <v>0.8236893599999999</v>
+        <v>0.8179672319999998</v>
       </c>
       <c r="P7">
-        <v>8.32841464</v>
+        <v>8.270557567999999</v>
       </c>
       <c r="Q7">
-        <v>10.05841464</v>
+        <v>10.000557568</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09556849041091886</v>
+        <v>0.09605246966088346</v>
       </c>
       <c r="T7">
-        <v>0.7241921765400956</v>
+        <v>0.731234664337861</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>29.78961672999975</v>
+        <v>24.82468060833312</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09303570148123046</v>
+        <v>0.09299268707208797</v>
       </c>
       <c r="C8">
-        <v>119.2619572442643</v>
+        <v>118.0725984219817</v>
       </c>
       <c r="D8">
-        <v>123.2959572442643</v>
+        <v>123.3705984219817</v>
       </c>
       <c r="E8">
-        <v>7.584</v>
+        <v>8.847999999999999</v>
       </c>
       <c r="F8">
-        <v>7.584</v>
+        <v>8.847999999999999</v>
       </c>
       <c r="G8">
         <v>3.55</v>
@@ -1943,28 +1943,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M8">
-        <v>0.3814752</v>
+        <v>0.4450543999999999</v>
       </c>
       <c r="N8">
-        <v>9.088524799999998</v>
+        <v>9.024945599999999</v>
       </c>
       <c r="O8">
-        <v>0.8179672319999998</v>
+        <v>0.8122451039999998</v>
       </c>
       <c r="P8">
-        <v>8.270557567999999</v>
+        <v>8.212700495999998</v>
       </c>
       <c r="Q8">
-        <v>10.000557568</v>
+        <v>9.942700495999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09605246966088346</v>
+        <v>0.09654685706676125</v>
       </c>
       <c r="T8">
-        <v>0.731234664337861</v>
+        <v>0.7384286034861157</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.82468060833312</v>
+        <v>21.27829766428554</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09299268707208797</v>
+        <v>0.09294967266294549</v>
       </c>
       <c r="C9">
-        <v>118.0725984219817</v>
+        <v>116.883330027323</v>
       </c>
       <c r="D9">
-        <v>123.3705984219817</v>
+        <v>123.445330027323</v>
       </c>
       <c r="E9">
-        <v>8.848000000000001</v>
+        <v>10.112</v>
       </c>
       <c r="F9">
-        <v>8.848000000000001</v>
+        <v>10.112</v>
       </c>
       <c r="G9">
         <v>3.55</v>
@@ -2025,28 +2025,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M9">
-        <v>0.4450544</v>
+        <v>0.5086336</v>
       </c>
       <c r="N9">
-        <v>9.024945599999999</v>
+        <v>8.961366399999999</v>
       </c>
       <c r="O9">
-        <v>0.8122451039999998</v>
+        <v>0.8065229759999999</v>
       </c>
       <c r="P9">
-        <v>8.212700495999998</v>
+        <v>8.154843423999999</v>
       </c>
       <c r="Q9">
-        <v>9.942700495999999</v>
+        <v>9.884843424</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09654685706676126</v>
+        <v>0.09705199202494075</v>
       </c>
       <c r="T9">
-        <v>0.7384286034861159</v>
+        <v>0.7457789326158546</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.27829766428553</v>
+        <v>18.61851045624984</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09294967266294549</v>
+        <v>0.09290665825380301</v>
       </c>
       <c r="C10">
-        <v>116.883330027323</v>
+        <v>115.6941522247171</v>
       </c>
       <c r="D10">
-        <v>123.445330027323</v>
+        <v>123.5201522247171</v>
       </c>
       <c r="E10">
-        <v>10.112</v>
+        <v>11.376</v>
       </c>
       <c r="F10">
-        <v>10.112</v>
+        <v>11.376</v>
       </c>
       <c r="G10">
         <v>3.55</v>
@@ -2107,28 +2107,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M10">
-        <v>0.5086336</v>
+        <v>0.5722128</v>
       </c>
       <c r="N10">
-        <v>8.961366399999999</v>
+        <v>8.8977872</v>
       </c>
       <c r="O10">
-        <v>0.8065229759999999</v>
+        <v>0.800800848</v>
       </c>
       <c r="P10">
-        <v>8.154843423999999</v>
+        <v>8.096986352</v>
       </c>
       <c r="Q10">
-        <v>9.884843424</v>
+        <v>9.826986352</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09705199202494075</v>
+        <v>0.09756822885033298</v>
       </c>
       <c r="T10">
-        <v>0.7457789326158546</v>
+        <v>0.7532908074407524</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.61851045624984</v>
+        <v>16.54978707222208</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09290665825380301</v>
+        <v>0.09286364384466053</v>
       </c>
       <c r="C11">
-        <v>115.6941522247171</v>
+        <v>114.5050651789917</v>
       </c>
       <c r="D11">
-        <v>123.5201522247171</v>
+        <v>123.5950651789917</v>
       </c>
       <c r="E11">
-        <v>11.376</v>
+        <v>12.64</v>
       </c>
       <c r="F11">
-        <v>11.376</v>
+        <v>12.64</v>
       </c>
       <c r="G11">
         <v>3.55</v>
@@ -2189,28 +2189,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M11">
-        <v>0.5722128</v>
+        <v>0.6357919999999999</v>
       </c>
       <c r="N11">
-        <v>8.8977872</v>
+        <v>8.834207999999999</v>
       </c>
       <c r="O11">
-        <v>0.800800848</v>
+        <v>0.7950787199999998</v>
       </c>
       <c r="P11">
-        <v>8.096986352</v>
+        <v>8.039129279999999</v>
       </c>
       <c r="Q11">
-        <v>9.826986352</v>
+        <v>9.76912928</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09756822885033298</v>
+        <v>0.09809593760517837</v>
       </c>
       <c r="T11">
-        <v>0.7532908074407524</v>
+        <v>0.7609696128173146</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.54978707222208</v>
+        <v>14.89480836499987</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09286364384466055</v>
+        <v>0.09282062943551805</v>
       </c>
       <c r="C12">
-        <v>114.5050651789917</v>
+        <v>113.3160690553748</v>
       </c>
       <c r="D12">
-        <v>123.5950651789917</v>
+        <v>123.6700690553748</v>
       </c>
       <c r="E12">
-        <v>12.64</v>
+        <v>13.904</v>
       </c>
       <c r="F12">
-        <v>12.64</v>
+        <v>13.904</v>
       </c>
       <c r="G12">
         <v>3.55</v>
@@ -2271,28 +2271,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M12">
-        <v>0.635792</v>
+        <v>0.6993712</v>
       </c>
       <c r="N12">
-        <v>8.834207999999999</v>
+        <v>8.770628799999999</v>
       </c>
       <c r="O12">
-        <v>0.7950787199999998</v>
+        <v>0.7893565919999999</v>
       </c>
       <c r="P12">
-        <v>8.039129279999999</v>
+        <v>7.981272207999999</v>
       </c>
       <c r="Q12">
-        <v>9.76912928</v>
+        <v>9.711272207999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09809593760517837</v>
+        <v>0.09863550498372815</v>
       </c>
       <c r="T12">
-        <v>0.7609696128173146</v>
+        <v>0.7688209756180692</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.89480836499987</v>
+        <v>13.54073487727261</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09282062943551805</v>
+        <v>0.09294141502637558</v>
       </c>
       <c r="C13">
-        <v>113.3160690553748</v>
+        <v>111.8416868922637</v>
       </c>
       <c r="D13">
-        <v>123.6700690553748</v>
+        <v>123.4596868922637</v>
       </c>
       <c r="E13">
-        <v>13.904</v>
+        <v>15.168</v>
       </c>
       <c r="F13">
-        <v>13.904</v>
+        <v>15.168</v>
       </c>
       <c r="G13">
         <v>3.55</v>
@@ -2353,45 +2353,45 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M13">
-        <v>0.6993712</v>
+        <v>0.7857023999999999</v>
       </c>
       <c r="N13">
-        <v>8.770628799999999</v>
+        <v>8.684297599999999</v>
       </c>
       <c r="O13">
-        <v>0.7893565919999999</v>
+        <v>0.7815867839999999</v>
       </c>
       <c r="P13">
-        <v>7.981272207999999</v>
+        <v>7.902710815999999</v>
       </c>
       <c r="Q13">
-        <v>9.711272207999999</v>
+        <v>9.632710815999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09863550498372815</v>
+        <v>0.09918733525724498</v>
       </c>
       <c r="T13">
-        <v>0.7688209756180692</v>
+        <v>0.7768507784824773</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.09</v>
       </c>
       <c r="W13">
-        <v>0.045773</v>
+        <v>0.047138</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.54073487727261</v>
+        <v>12.05290960037796</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09294141502637558</v>
+        <v>0.09291205061723311</v>
       </c>
       <c r="C14">
-        <v>111.8416868922637</v>
+        <v>110.6287674077582</v>
       </c>
       <c r="D14">
-        <v>123.4596868922637</v>
+        <v>123.5107674077582</v>
       </c>
       <c r="E14">
-        <v>15.168</v>
+        <v>16.432</v>
       </c>
       <c r="F14">
-        <v>15.168</v>
+        <v>16.432</v>
       </c>
       <c r="G14">
         <v>3.55</v>
@@ -2435,28 +2435,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M14">
-        <v>0.7857023999999999</v>
+        <v>0.8511776000000001</v>
       </c>
       <c r="N14">
-        <v>8.684297599999999</v>
+        <v>8.618822399999999</v>
       </c>
       <c r="O14">
-        <v>0.7815867839999999</v>
+        <v>0.7756940159999999</v>
       </c>
       <c r="P14">
-        <v>7.902710815999999</v>
+        <v>7.843128383999999</v>
       </c>
       <c r="Q14">
-        <v>9.632710815999999</v>
+        <v>9.573128383999999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09918733525724498</v>
+        <v>0.09975185128417599</v>
       </c>
       <c r="T14">
-        <v>0.7768507784824773</v>
+        <v>0.7850651745161822</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.05290960037796</v>
+        <v>11.12576270804119</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09291205061723311</v>
+        <v>0.09288268620809063</v>
       </c>
       <c r="C15">
-        <v>110.6287674077582</v>
+        <v>109.4158902091051</v>
       </c>
       <c r="D15">
-        <v>123.5107674077582</v>
+        <v>123.5618902091051</v>
       </c>
       <c r="E15">
-        <v>16.432</v>
+        <v>17.696</v>
       </c>
       <c r="F15">
-        <v>16.432</v>
+        <v>17.696</v>
       </c>
       <c r="G15">
         <v>3.55</v>
@@ -2517,28 +2517,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M15">
-        <v>0.8511776000000001</v>
+        <v>0.9166528</v>
       </c>
       <c r="N15">
-        <v>8.618822399999999</v>
+        <v>8.553347199999999</v>
       </c>
       <c r="O15">
-        <v>0.7756940159999999</v>
+        <v>0.7698012479999999</v>
       </c>
       <c r="P15">
-        <v>7.843128383999999</v>
+        <v>7.783545951999999</v>
       </c>
       <c r="Q15">
-        <v>9.573128383999999</v>
+        <v>9.513545951999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09975185128417599</v>
+        <v>0.1003294955908031</v>
       </c>
       <c r="T15">
-        <v>0.7850651745161822</v>
+        <v>0.7934706030157872</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.12576270804119</v>
+        <v>10.33106537175253</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09288268620809063</v>
+        <v>0.09308537179894814</v>
       </c>
       <c r="C16">
-        <v>109.4158902091051</v>
+        <v>107.7998786198808</v>
       </c>
       <c r="D16">
-        <v>123.5618902091051</v>
+        <v>123.2098786198808</v>
       </c>
       <c r="E16">
-        <v>17.696</v>
+        <v>18.96</v>
       </c>
       <c r="F16">
-        <v>17.696</v>
+        <v>18.96</v>
       </c>
       <c r="G16">
         <v>3.55</v>
@@ -2599,45 +2599,45 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M16">
-        <v>0.9166528</v>
+        <v>1.01436</v>
       </c>
       <c r="N16">
-        <v>8.553347199999999</v>
+        <v>8.455639999999999</v>
       </c>
       <c r="O16">
-        <v>0.7698012479999999</v>
+        <v>0.7610075999999999</v>
       </c>
       <c r="P16">
-        <v>7.783545951999999</v>
+        <v>7.694632399999999</v>
       </c>
       <c r="Q16">
-        <v>9.513545951999999</v>
+        <v>9.424632399999998</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1003294955908031</v>
+        <v>0.1009207315281743</v>
       </c>
       <c r="T16">
-        <v>0.7934706030157872</v>
+        <v>0.8020738063036182</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.09</v>
       </c>
       <c r="W16">
-        <v>0.047138</v>
+        <v>0.048685</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.33106537175253</v>
+        <v>9.335935959619857</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09308537179894814</v>
+        <v>0.09307147738980567</v>
       </c>
       <c r="C17">
-        <v>107.7998786198808</v>
+        <v>106.5599455102526</v>
       </c>
       <c r="D17">
-        <v>123.2098786198808</v>
+        <v>123.2339455102526</v>
       </c>
       <c r="E17">
-        <v>18.96</v>
+        <v>20.224</v>
       </c>
       <c r="F17">
-        <v>18.96</v>
+        <v>20.224</v>
       </c>
       <c r="G17">
         <v>3.55</v>
@@ -2681,28 +2681,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M17">
-        <v>1.01436</v>
+        <v>1.081984</v>
       </c>
       <c r="N17">
-        <v>8.455639999999999</v>
+        <v>8.388015999999999</v>
       </c>
       <c r="O17">
-        <v>0.7610075999999999</v>
+        <v>0.7549214399999998</v>
       </c>
       <c r="P17">
-        <v>7.694632399999999</v>
+        <v>7.633094559999999</v>
       </c>
       <c r="Q17">
-        <v>9.424632399999998</v>
+        <v>9.363094559999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1009207315281743</v>
+        <v>0.1015260445116734</v>
       </c>
       <c r="T17">
-        <v>0.8020738063036182</v>
+        <v>0.810881847764969</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.335935959619858</v>
+        <v>8.752439962143615</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09307147738980567</v>
+        <v>0.0930575829806632</v>
       </c>
       <c r="C18">
-        <v>106.5599455102526</v>
+        <v>105.3200218045518</v>
       </c>
       <c r="D18">
-        <v>123.2339455102526</v>
+        <v>123.2580218045518</v>
       </c>
       <c r="E18">
-        <v>20.224</v>
+        <v>21.488</v>
       </c>
       <c r="F18">
-        <v>20.224</v>
+        <v>21.488</v>
       </c>
       <c r="G18">
         <v>3.55</v>
@@ -2763,28 +2763,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M18">
-        <v>1.081984</v>
+        <v>1.149608</v>
       </c>
       <c r="N18">
-        <v>8.388015999999999</v>
+        <v>8.320391999999998</v>
       </c>
       <c r="O18">
-        <v>0.7549214399999998</v>
+        <v>0.7488352799999998</v>
       </c>
       <c r="P18">
-        <v>7.633094559999999</v>
+        <v>7.571556719999998</v>
       </c>
       <c r="Q18">
-        <v>9.363094559999999</v>
+        <v>9.301556719999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1015260445116734</v>
+        <v>0.1021459433501966</v>
       </c>
       <c r="T18">
-        <v>0.810881847764969</v>
+        <v>0.8199021311892438</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.752439962143615</v>
+        <v>8.237590552605756</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0930575829806632</v>
+        <v>0.09304368857152072</v>
       </c>
       <c r="C19">
-        <v>105.3200218045518</v>
+        <v>104.0801075082911</v>
       </c>
       <c r="D19">
-        <v>123.2580218045518</v>
+        <v>123.2821075082911</v>
       </c>
       <c r="E19">
-        <v>21.488</v>
+        <v>22.752</v>
       </c>
       <c r="F19">
-        <v>21.488</v>
+        <v>22.752</v>
       </c>
       <c r="G19">
         <v>3.55</v>
@@ -2845,28 +2845,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M19">
-        <v>1.149608</v>
+        <v>1.217232</v>
       </c>
       <c r="N19">
-        <v>8.320391999999998</v>
+        <v>8.252768</v>
       </c>
       <c r="O19">
-        <v>0.7488352799999998</v>
+        <v>0.7427491199999999</v>
       </c>
       <c r="P19">
-        <v>7.571556719999998</v>
+        <v>7.51001888</v>
       </c>
       <c r="Q19">
-        <v>9.301556719999999</v>
+        <v>9.240018879999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1021459433501966</v>
+        <v>0.1027809616725862</v>
       </c>
       <c r="T19">
-        <v>0.8199021311892438</v>
+        <v>0.8291424215263059</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.237590552605756</v>
+        <v>7.779946633016548</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09304368857152072</v>
+        <v>0.09316811416237825</v>
       </c>
       <c r="C20">
-        <v>104.0801075082911</v>
+        <v>102.6007527278666</v>
       </c>
       <c r="D20">
-        <v>123.2821075082911</v>
+        <v>123.0667527278666</v>
       </c>
       <c r="E20">
-        <v>22.752</v>
+        <v>24.016</v>
       </c>
       <c r="F20">
-        <v>22.752</v>
+        <v>24.016</v>
       </c>
       <c r="G20">
         <v>3.55</v>
@@ -2927,45 +2927,45 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M20">
-        <v>1.217232</v>
+        <v>1.3040688</v>
       </c>
       <c r="N20">
-        <v>8.252768</v>
+        <v>8.165931199999999</v>
       </c>
       <c r="O20">
-        <v>0.7427491199999999</v>
+        <v>0.7349338079999999</v>
       </c>
       <c r="P20">
-        <v>7.51001888</v>
+        <v>7.430997391999999</v>
       </c>
       <c r="Q20">
-        <v>9.240018879999999</v>
+        <v>9.160997391999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1027809616725862</v>
+        <v>0.1034316594597262</v>
       </c>
       <c r="T20">
-        <v>0.8291424215263059</v>
+        <v>0.8386108671803324</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.09</v>
       </c>
       <c r="W20">
-        <v>0.048685</v>
+        <v>0.04941300000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.779946633016549</v>
+        <v>7.261886796156767</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09316811416237825</v>
+        <v>0.09316149975323577</v>
       </c>
       <c r="C21">
-        <v>102.6007527278666</v>
+        <v>101.3481819554997</v>
       </c>
       <c r="D21">
-        <v>123.0667527278666</v>
+        <v>123.0781819554997</v>
       </c>
       <c r="E21">
-        <v>24.016</v>
+        <v>25.28</v>
       </c>
       <c r="F21">
-        <v>24.016</v>
+        <v>25.28</v>
       </c>
       <c r="G21">
         <v>3.55</v>
@@ -3009,28 +3009,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M21">
-        <v>1.3040688</v>
+        <v>1.372704</v>
       </c>
       <c r="N21">
-        <v>8.165931199999999</v>
+        <v>8.097295999999998</v>
       </c>
       <c r="O21">
-        <v>0.7349338079999999</v>
+        <v>0.7287566399999998</v>
       </c>
       <c r="P21">
-        <v>7.430997391999999</v>
+        <v>7.368539359999998</v>
       </c>
       <c r="Q21">
-        <v>9.160997391999999</v>
+        <v>9.098539359999998</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1034316594597262</v>
+        <v>0.1040986246915447</v>
       </c>
       <c r="T21">
-        <v>0.8386108671803324</v>
+        <v>0.8483160239757097</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.261886796156767</v>
+        <v>6.898792456348927</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09316149975323577</v>
+        <v>0.0931548853440933</v>
       </c>
       <c r="C22">
-        <v>101.3481819554997</v>
+        <v>100.095613306198</v>
       </c>
       <c r="D22">
-        <v>123.0781819554997</v>
+        <v>123.089613306198</v>
       </c>
       <c r="E22">
-        <v>25.28</v>
+        <v>26.544</v>
       </c>
       <c r="F22">
-        <v>25.28</v>
+        <v>26.544</v>
       </c>
       <c r="G22">
         <v>3.55</v>
@@ -3091,28 +3091,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M22">
-        <v>1.372704</v>
+        <v>1.4413392</v>
       </c>
       <c r="N22">
-        <v>8.097295999999998</v>
+        <v>8.028660799999999</v>
       </c>
       <c r="O22">
-        <v>0.7287566399999998</v>
+        <v>0.7225794719999998</v>
       </c>
       <c r="P22">
-        <v>7.368539359999998</v>
+        <v>7.306081327999999</v>
       </c>
       <c r="Q22">
-        <v>9.098539359999998</v>
+        <v>9.036081328</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1040986246915447</v>
+        <v>0.1047824751191054</v>
       </c>
       <c r="T22">
-        <v>0.8483160239757097</v>
+        <v>0.8582668809431218</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.898792456348927</v>
+        <v>6.570278529856121</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0931548853440933</v>
+        <v>0.09314827093495082</v>
       </c>
       <c r="C23">
-        <v>100.095613306198</v>
+        <v>98.84304678055335</v>
       </c>
       <c r="D23">
-        <v>123.089613306198</v>
+        <v>123.1010467805534</v>
       </c>
       <c r="E23">
-        <v>26.544</v>
+        <v>27.808</v>
       </c>
       <c r="F23">
-        <v>26.544</v>
+        <v>27.808</v>
       </c>
       <c r="G23">
         <v>3.55</v>
@@ -3173,28 +3173,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M23">
-        <v>1.4413392</v>
+        <v>1.5099744</v>
       </c>
       <c r="N23">
-        <v>8.028660799999999</v>
+        <v>7.960025599999999</v>
       </c>
       <c r="O23">
-        <v>0.7225794719999998</v>
+        <v>0.7164023039999998</v>
       </c>
       <c r="P23">
-        <v>7.306081327999999</v>
+        <v>7.243623295999999</v>
       </c>
       <c r="Q23">
-        <v>9.036081328</v>
+        <v>8.973623296</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1047824751191054</v>
+        <v>0.1054838601730139</v>
       </c>
       <c r="T23">
-        <v>0.8582668809431218</v>
+        <v>0.8684728880891854</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.570278529856122</v>
+        <v>6.271629505771753</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09314827093495082</v>
+        <v>0.09335095652580833</v>
       </c>
       <c r="C24">
-        <v>98.84304678055335</v>
+        <v>97.2296523470538</v>
       </c>
       <c r="D24">
-        <v>123.1010467805534</v>
+        <v>122.7516523470538</v>
       </c>
       <c r="E24">
-        <v>27.808</v>
+        <v>29.072</v>
       </c>
       <c r="F24">
-        <v>27.808</v>
+        <v>29.072</v>
       </c>
       <c r="G24">
         <v>3.55</v>
@@ -3255,45 +3255,45 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M24">
-        <v>1.5099744</v>
+        <v>1.6076816</v>
       </c>
       <c r="N24">
-        <v>7.960025599999999</v>
+        <v>7.862318399999999</v>
       </c>
       <c r="O24">
-        <v>0.7164023039999998</v>
+        <v>0.7076086559999999</v>
       </c>
       <c r="P24">
-        <v>7.243623295999999</v>
+        <v>7.154709743999999</v>
       </c>
       <c r="Q24">
-        <v>8.973623296</v>
+        <v>8.884709743999998</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1054838601730139</v>
+        <v>0.1062034630205303</v>
       </c>
       <c r="T24">
-        <v>0.8684728880891854</v>
+        <v>0.8789439863299521</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.09</v>
       </c>
       <c r="W24">
-        <v>0.04941300000000001</v>
+        <v>0.05032300000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.271629505771753</v>
+        <v>5.890469854229841</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09335095652580833</v>
+        <v>0.09335344211666588</v>
       </c>
       <c r="C25">
-        <v>97.2296523470538</v>
+        <v>95.96137993399371</v>
       </c>
       <c r="D25">
-        <v>122.7516523470538</v>
+        <v>122.7473799339937</v>
       </c>
       <c r="E25">
-        <v>29.072</v>
+        <v>30.336</v>
       </c>
       <c r="F25">
-        <v>29.072</v>
+        <v>30.336</v>
       </c>
       <c r="G25">
         <v>3.55</v>
@@ -3337,28 +3337,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M25">
-        <v>1.6076816</v>
+        <v>1.6775808</v>
       </c>
       <c r="N25">
-        <v>7.862318399999999</v>
+        <v>7.792419199999999</v>
       </c>
       <c r="O25">
-        <v>0.7076086559999999</v>
+        <v>0.7013177279999998</v>
       </c>
       <c r="P25">
-        <v>7.154709743999999</v>
+        <v>7.091101471999998</v>
       </c>
       <c r="Q25">
-        <v>8.884709743999998</v>
+        <v>8.821101471999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1062034630205303</v>
+        <v>0.1069420027850867</v>
       </c>
       <c r="T25">
-        <v>0.8789439863299521</v>
+        <v>0.8896906397875811</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.890469854229841</v>
+        <v>5.645033610303598</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09335344211666585</v>
+        <v>0.09335592770752338</v>
       </c>
       <c r="C26">
-        <v>95.96137993399375</v>
+        <v>94.69310781832894</v>
       </c>
       <c r="D26">
-        <v>122.7473799339938</v>
+        <v>122.7431078183289</v>
       </c>
       <c r="E26">
-        <v>30.336</v>
+        <v>31.6</v>
       </c>
       <c r="F26">
-        <v>30.336</v>
+        <v>31.6</v>
       </c>
       <c r="G26">
         <v>3.55</v>
@@ -3419,28 +3419,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M26">
-        <v>1.6775808</v>
+        <v>1.74748</v>
       </c>
       <c r="N26">
-        <v>7.792419199999999</v>
+        <v>7.722519999999998</v>
       </c>
       <c r="O26">
-        <v>0.7013177279999999</v>
+        <v>0.6950267999999998</v>
       </c>
       <c r="P26">
-        <v>7.091101471999999</v>
+        <v>7.027493199999999</v>
       </c>
       <c r="Q26">
-        <v>8.821101471999999</v>
+        <v>8.757493199999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1069420027850867</v>
+        <v>0.1077002369433645</v>
       </c>
       <c r="T26">
-        <v>0.889690639787581</v>
+        <v>0.9007238706707467</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.645033610303599</v>
+        <v>5.419232265891454</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09335592770752338</v>
+        <v>0.0933584132983809</v>
       </c>
       <c r="C27">
-        <v>94.69310781832894</v>
+        <v>93.42483600002829</v>
       </c>
       <c r="D27">
-        <v>122.7431078183289</v>
+        <v>122.7388360000283</v>
       </c>
       <c r="E27">
-        <v>31.6</v>
+        <v>32.864</v>
       </c>
       <c r="F27">
-        <v>31.6</v>
+        <v>32.864</v>
       </c>
       <c r="G27">
         <v>3.55</v>
@@ -3501,28 +3501,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M27">
-        <v>1.74748</v>
+        <v>1.8173792</v>
       </c>
       <c r="N27">
-        <v>7.722519999999998</v>
+        <v>7.652620799999998</v>
       </c>
       <c r="O27">
-        <v>0.6950267999999998</v>
+        <v>0.6887358719999999</v>
       </c>
       <c r="P27">
-        <v>7.027493199999999</v>
+        <v>6.963884927999999</v>
       </c>
       <c r="Q27">
-        <v>8.757493199999999</v>
+        <v>8.693884927999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1077002369433645</v>
+        <v>0.108478963916731</v>
       </c>
       <c r="T27">
-        <v>0.9007238706707467</v>
+        <v>0.9120552969831871</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.419232265891454</v>
+        <v>5.21080025566486</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0933584132983809</v>
+        <v>0.09336089888923844</v>
       </c>
       <c r="C28">
-        <v>93.42483600002829</v>
+        <v>92.15656447906076</v>
       </c>
       <c r="D28">
-        <v>122.7388360000283</v>
+        <v>122.7345644790608</v>
       </c>
       <c r="E28">
-        <v>32.864</v>
+        <v>34.12800000000001</v>
       </c>
       <c r="F28">
-        <v>32.864</v>
+        <v>34.12800000000001</v>
       </c>
       <c r="G28">
         <v>3.55</v>
@@ -3583,28 +3583,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M28">
-        <v>1.8173792</v>
+        <v>1.8872784</v>
       </c>
       <c r="N28">
-        <v>7.652620799999998</v>
+        <v>7.582721599999998</v>
       </c>
       <c r="O28">
-        <v>0.6887358719999999</v>
+        <v>0.6824449439999998</v>
       </c>
       <c r="P28">
-        <v>6.963884927999999</v>
+        <v>6.900276655999999</v>
       </c>
       <c r="Q28">
-        <v>8.693884927999999</v>
+        <v>8.630276655999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.108478963916731</v>
+        <v>0.1092790258756691</v>
       </c>
       <c r="T28">
-        <v>0.9120552969831871</v>
+        <v>0.9236971733315849</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.21080025566486</v>
+        <v>5.017807653603198</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09336089888923844</v>
+        <v>0.09336338448009596</v>
       </c>
       <c r="C29">
-        <v>92.15656447906076</v>
+        <v>90.88829325539538</v>
       </c>
       <c r="D29">
-        <v>122.7345644790608</v>
+        <v>122.7302932553954</v>
       </c>
       <c r="E29">
-        <v>34.12800000000001</v>
+        <v>35.392</v>
       </c>
       <c r="F29">
-        <v>34.12800000000001</v>
+        <v>35.392</v>
       </c>
       <c r="G29">
         <v>3.55</v>
@@ -3665,28 +3665,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M29">
-        <v>1.8872784</v>
+        <v>1.9571776</v>
       </c>
       <c r="N29">
-        <v>7.582721599999998</v>
+        <v>7.512822399999998</v>
       </c>
       <c r="O29">
-        <v>0.6824449439999998</v>
+        <v>0.6761540159999998</v>
       </c>
       <c r="P29">
-        <v>6.900276655999999</v>
+        <v>6.836668383999998</v>
       </c>
       <c r="Q29">
-        <v>8.630276655999999</v>
+        <v>8.566668383999998</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1092790258756691</v>
+        <v>0.110101311777911</v>
       </c>
       <c r="T29">
-        <v>0.9236971733315849</v>
+        <v>0.9356624351341047</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.017807653603198</v>
+        <v>4.838600237403083</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09336338448009596</v>
+        <v>0.09336587007095348</v>
       </c>
       <c r="C30">
-        <v>90.88829325539538</v>
+        <v>89.62002232900103</v>
       </c>
       <c r="D30">
-        <v>122.7302932553954</v>
+        <v>122.726022329001</v>
       </c>
       <c r="E30">
-        <v>35.392</v>
+        <v>36.65600000000001</v>
       </c>
       <c r="F30">
-        <v>35.392</v>
+        <v>36.65600000000001</v>
       </c>
       <c r="G30">
         <v>3.55</v>
@@ -3747,28 +3747,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M30">
-        <v>1.9571776</v>
+        <v>2.027076800000001</v>
       </c>
       <c r="N30">
-        <v>7.512822399999998</v>
+        <v>7.442923199999998</v>
       </c>
       <c r="O30">
-        <v>0.6761540159999998</v>
+        <v>0.6698630879999998</v>
       </c>
       <c r="P30">
-        <v>6.836668383999998</v>
+        <v>6.773060111999999</v>
       </c>
       <c r="Q30">
-        <v>8.566668383999998</v>
+        <v>8.503060111999998</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.110101311777911</v>
+        <v>0.1109467606633148</v>
       </c>
       <c r="T30">
-        <v>0.9356624351341047</v>
+        <v>0.9479647465648647</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.838600237403083</v>
+        <v>4.671751953354701</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09336587007095348</v>
+        <v>0.09336835566181101</v>
       </c>
       <c r="C31">
-        <v>89.62002232900105</v>
+        <v>88.3517516998467</v>
       </c>
       <c r="D31">
-        <v>122.726022329001</v>
+        <v>122.7217516998467</v>
       </c>
       <c r="E31">
-        <v>36.656</v>
+        <v>37.92</v>
       </c>
       <c r="F31">
-        <v>36.656</v>
+        <v>37.92</v>
       </c>
       <c r="G31">
         <v>3.55</v>
@@ -3829,28 +3829,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M31">
-        <v>2.0270768</v>
+        <v>2.096976</v>
       </c>
       <c r="N31">
-        <v>7.442923199999999</v>
+        <v>7.373023999999999</v>
       </c>
       <c r="O31">
-        <v>0.6698630879999999</v>
+        <v>0.6635721599999999</v>
       </c>
       <c r="P31">
-        <v>6.773060112</v>
+        <v>6.709451839999999</v>
       </c>
       <c r="Q31">
-        <v>8.503060112</v>
+        <v>8.439451839999998</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1109467606633148</v>
+        <v>0.1118163652311586</v>
       </c>
       <c r="T31">
-        <v>0.9479647465648646</v>
+        <v>0.9606185526079321</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.671751953354702</v>
+        <v>4.516026888242878</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09336835566181101</v>
+        <v>0.09407609125266853</v>
       </c>
       <c r="C32">
-        <v>88.3517516998467</v>
+        <v>85.8837247039805</v>
       </c>
       <c r="D32">
-        <v>122.7217516998467</v>
+        <v>121.5177247039805</v>
       </c>
       <c r="E32">
-        <v>37.92</v>
+        <v>39.184</v>
       </c>
       <c r="F32">
-        <v>37.92</v>
+        <v>39.184</v>
       </c>
       <c r="G32">
         <v>3.55</v>
@@ -3911,45 +3911,45 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M32">
-        <v>2.096976</v>
+        <v>2.2648352</v>
       </c>
       <c r="N32">
-        <v>7.373023999999999</v>
+        <v>7.205164799999999</v>
       </c>
       <c r="O32">
-        <v>0.6635721599999999</v>
+        <v>0.6484648319999998</v>
       </c>
       <c r="P32">
-        <v>6.709451839999999</v>
+        <v>6.556699967999998</v>
       </c>
       <c r="Q32">
-        <v>8.439451839999998</v>
+        <v>8.286699967999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1118163652311586</v>
+        <v>0.1127111757285051</v>
       </c>
       <c r="T32">
-        <v>0.9606185526079321</v>
+        <v>0.9736391356377547</v>
       </c>
       <c r="U32">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V32">
         <v>0.09</v>
       </c>
       <c r="W32">
-        <v>0.05032300000000001</v>
+        <v>0.05259800000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.516026888242878</v>
+        <v>4.181319682774269</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09407609125266853</v>
+        <v>0.09410132684352605</v>
       </c>
       <c r="C33">
-        <v>85.8837247039805</v>
+        <v>84.57722901773877</v>
       </c>
       <c r="D33">
-        <v>121.5177247039805</v>
+        <v>121.4752290177388</v>
       </c>
       <c r="E33">
-        <v>39.184</v>
+        <v>40.448</v>
       </c>
       <c r="F33">
-        <v>39.184</v>
+        <v>40.448</v>
       </c>
       <c r="G33">
         <v>3.55</v>
@@ -3993,28 +3993,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M33">
-        <v>2.2648352</v>
+        <v>2.3378944</v>
       </c>
       <c r="N33">
-        <v>7.205164799999999</v>
+        <v>7.132105599999999</v>
       </c>
       <c r="O33">
-        <v>0.6484648319999998</v>
+        <v>0.6418895039999999</v>
       </c>
       <c r="P33">
-        <v>6.556699967999998</v>
+        <v>6.490216095999999</v>
       </c>
       <c r="Q33">
-        <v>8.286699967999999</v>
+        <v>8.220216096</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1127111757285051</v>
+        <v>0.113632304181656</v>
       </c>
       <c r="T33">
-        <v>0.9736391356377547</v>
+        <v>0.9870426769919842</v>
       </c>
       <c r="U33">
         <v>0.0578</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.181319682774269</v>
+        <v>4.050653442687573</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09410132684352605</v>
+        <v>0.09517761243438355</v>
       </c>
       <c r="C34">
-        <v>84.57722901773877</v>
+        <v>81.52806806023406</v>
       </c>
       <c r="D34">
-        <v>121.4752290177388</v>
+        <v>119.6900680602341</v>
       </c>
       <c r="E34">
-        <v>40.448</v>
+        <v>41.712</v>
       </c>
       <c r="F34">
-        <v>40.448</v>
+        <v>41.712</v>
       </c>
       <c r="G34">
         <v>3.55</v>
@@ -4075,45 +4075,45 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M34">
-        <v>2.3378944</v>
+        <v>2.5569456</v>
       </c>
       <c r="N34">
-        <v>7.132105599999999</v>
+        <v>6.913054399999998</v>
       </c>
       <c r="O34">
-        <v>0.6418895039999999</v>
+        <v>0.6221748959999999</v>
       </c>
       <c r="P34">
-        <v>6.490216095999999</v>
+        <v>6.290879503999999</v>
       </c>
       <c r="Q34">
-        <v>8.220216096</v>
+        <v>8.020879503999998</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.113632304181656</v>
+        <v>0.1145809290065426</v>
       </c>
       <c r="T34">
-        <v>0.9870426769919842</v>
+        <v>1.00084632405828</v>
       </c>
       <c r="U34">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V34">
         <v>0.09</v>
       </c>
       <c r="W34">
-        <v>0.05259800000000001</v>
+        <v>0.055783</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.050653442687573</v>
+        <v>3.703637652674346</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09517761243438355</v>
+        <v>0.09523469802524111</v>
       </c>
       <c r="C35">
-        <v>81.52806806023406</v>
+        <v>80.17084821820441</v>
       </c>
       <c r="D35">
-        <v>119.6900680602341</v>
+        <v>119.5968482182044</v>
       </c>
       <c r="E35">
-        <v>41.712</v>
+        <v>42.97600000000001</v>
       </c>
       <c r="F35">
-        <v>41.712</v>
+        <v>42.97600000000001</v>
       </c>
       <c r="G35">
         <v>3.55</v>
@@ -4157,28 +4157,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M35">
-        <v>2.5569456</v>
+        <v>2.6344288</v>
       </c>
       <c r="N35">
-        <v>6.913054399999998</v>
+        <v>6.835571199999999</v>
       </c>
       <c r="O35">
-        <v>0.6221748959999999</v>
+        <v>0.6152014079999999</v>
       </c>
       <c r="P35">
-        <v>6.290879503999999</v>
+        <v>6.220369791999999</v>
       </c>
       <c r="Q35">
-        <v>8.020879503999998</v>
+        <v>7.950369791999998</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1145809290065426</v>
+        <v>0.1155583000382441</v>
       </c>
       <c r="T35">
-        <v>1.00084632405828</v>
+        <v>1.015068263459919</v>
       </c>
       <c r="U35">
         <v>0.0613</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.703637652674346</v>
+        <v>3.594707133478042</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09523469802524111</v>
+        <v>0.09618358361609861</v>
       </c>
       <c r="C36">
-        <v>80.17084821820441</v>
+        <v>77.37832860656916</v>
       </c>
       <c r="D36">
-        <v>119.5968482182044</v>
+        <v>118.0683286065692</v>
       </c>
       <c r="E36">
-        <v>42.97600000000001</v>
+        <v>44.24000000000001</v>
       </c>
       <c r="F36">
-        <v>42.97600000000001</v>
+        <v>44.24000000000001</v>
       </c>
       <c r="G36">
         <v>3.55</v>
@@ -4239,45 +4239,45 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M36">
-        <v>2.6344288</v>
+        <v>2.835784000000001</v>
       </c>
       <c r="N36">
-        <v>6.835571199999999</v>
+        <v>6.634215999999999</v>
       </c>
       <c r="O36">
-        <v>0.6152014079999999</v>
+        <v>0.5970794399999998</v>
       </c>
       <c r="P36">
-        <v>6.220369791999999</v>
+        <v>6.037136559999999</v>
       </c>
       <c r="Q36">
-        <v>7.950369791999998</v>
+        <v>7.767136559999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1155583000382441</v>
+        <v>0.1165657440247671</v>
       </c>
       <c r="T36">
-        <v>1.015068263459919</v>
+        <v>1.029727800996992</v>
       </c>
       <c r="U36">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V36">
         <v>0.09</v>
       </c>
       <c r="W36">
-        <v>0.055783</v>
+        <v>0.05833100000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.594707133478042</v>
+        <v>3.339464500822346</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09618358361609861</v>
+        <v>0.09626614920695613</v>
       </c>
       <c r="C37">
-        <v>77.37832860656916</v>
+        <v>75.983172886861</v>
       </c>
       <c r="D37">
-        <v>118.0683286065692</v>
+        <v>117.937172886861</v>
       </c>
       <c r="E37">
-        <v>44.24000000000001</v>
+        <v>45.504</v>
       </c>
       <c r="F37">
-        <v>44.24000000000001</v>
+        <v>45.504</v>
       </c>
       <c r="G37">
         <v>3.55</v>
@@ -4321,28 +4321,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M37">
-        <v>2.835784000000001</v>
+        <v>2.9168064</v>
       </c>
       <c r="N37">
-        <v>6.634215999999999</v>
+        <v>6.553193599999998</v>
       </c>
       <c r="O37">
-        <v>0.5970794399999998</v>
+        <v>0.5897874239999998</v>
       </c>
       <c r="P37">
-        <v>6.037136559999999</v>
+        <v>5.963406175999999</v>
       </c>
       <c r="Q37">
-        <v>7.767136559999999</v>
+        <v>7.693406175999998</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1165657440247671</v>
+        <v>0.117604670635869</v>
       </c>
       <c r="T37">
-        <v>1.029727800996992</v>
+        <v>1.044845449082099</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.339464500822346</v>
+        <v>3.246701598021726</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09626614920695614</v>
+        <v>0.09634871479781366</v>
       </c>
       <c r="C38">
-        <v>75.98317288686098</v>
+        <v>74.58830823141439</v>
       </c>
       <c r="D38">
-        <v>117.937172886861</v>
+        <v>117.8063082314144</v>
       </c>
       <c r="E38">
-        <v>45.504</v>
+        <v>46.768</v>
       </c>
       <c r="F38">
-        <v>45.504</v>
+        <v>46.768</v>
       </c>
       <c r="G38">
         <v>3.55</v>
@@ -4403,28 +4403,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M38">
-        <v>2.9168064</v>
+        <v>2.9978288</v>
       </c>
       <c r="N38">
-        <v>6.553193599999998</v>
+        <v>6.472171199999998</v>
       </c>
       <c r="O38">
-        <v>0.5897874239999998</v>
+        <v>0.5824954079999998</v>
       </c>
       <c r="P38">
-        <v>5.963406175999999</v>
+        <v>5.889675791999998</v>
       </c>
       <c r="Q38">
-        <v>7.693406175999998</v>
+        <v>7.619675791999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.117604670635869</v>
+        <v>0.1186765790441487</v>
       </c>
       <c r="T38">
-        <v>1.044845449082099</v>
+        <v>1.060443022503241</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.246701598021726</v>
+        <v>3.158952906183301</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09634871479781366</v>
+        <v>0.09643128038867119</v>
       </c>
       <c r="C39">
-        <v>74.58830823141439</v>
+        <v>73.19373367239697</v>
       </c>
       <c r="D39">
-        <v>117.8063082314144</v>
+        <v>117.675733672397</v>
       </c>
       <c r="E39">
-        <v>46.768</v>
+        <v>48.032</v>
       </c>
       <c r="F39">
-        <v>46.768</v>
+        <v>48.032</v>
       </c>
       <c r="G39">
         <v>3.55</v>
@@ -4485,28 +4485,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M39">
-        <v>2.9978288</v>
+        <v>3.0788512</v>
       </c>
       <c r="N39">
-        <v>6.472171199999998</v>
+        <v>6.391148799999998</v>
       </c>
       <c r="O39">
-        <v>0.5824954079999998</v>
+        <v>0.5752033919999998</v>
       </c>
       <c r="P39">
-        <v>5.889675791999998</v>
+        <v>5.815945407999998</v>
       </c>
       <c r="Q39">
-        <v>7.619675791999999</v>
+        <v>7.545945407999998</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1186765790441487</v>
+        <v>0.119783065143018</v>
       </c>
       <c r="T39">
-        <v>1.060443022503241</v>
+        <v>1.076543743454097</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.158952906183301</v>
+        <v>3.075822566546898</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09643128038867119</v>
+        <v>0.09928206597952871</v>
       </c>
       <c r="C40">
-        <v>73.19373367239697</v>
+        <v>67.59230643753581</v>
       </c>
       <c r="D40">
-        <v>117.675733672397</v>
+        <v>113.3383064375358</v>
       </c>
       <c r="E40">
-        <v>48.032</v>
+        <v>49.29600000000001</v>
       </c>
       <c r="F40">
-        <v>48.032</v>
+        <v>49.29600000000001</v>
       </c>
       <c r="G40">
         <v>3.55</v>
@@ -4567,45 +4567,45 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M40">
-        <v>3.0788512</v>
+        <v>3.544382400000001</v>
       </c>
       <c r="N40">
-        <v>6.391148799999998</v>
+        <v>5.925617599999998</v>
       </c>
       <c r="O40">
-        <v>0.5752033919999998</v>
+        <v>0.5333055839999998</v>
       </c>
       <c r="P40">
-        <v>5.815945407999998</v>
+        <v>5.392312015999998</v>
       </c>
       <c r="Q40">
-        <v>7.545945407999998</v>
+        <v>7.122312015999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.119783065143018</v>
+        <v>0.1209258294746372</v>
       </c>
       <c r="T40">
-        <v>1.076543743454097</v>
+        <v>1.093172356895145</v>
       </c>
       <c r="U40">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V40">
         <v>0.09</v>
       </c>
       <c r="W40">
-        <v>0.05833100000000001</v>
+        <v>0.065429</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.075822566546898</v>
+        <v>2.67183360350734</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09928206597952871</v>
+        <v>0.09943561157038623</v>
       </c>
       <c r="C41">
-        <v>67.59230643753581</v>
+        <v>66.10374588556689</v>
       </c>
       <c r="D41">
-        <v>113.3383064375358</v>
+        <v>113.1137458855669</v>
       </c>
       <c r="E41">
-        <v>49.29600000000001</v>
+        <v>50.56</v>
       </c>
       <c r="F41">
-        <v>49.29600000000001</v>
+        <v>50.56</v>
       </c>
       <c r="G41">
         <v>3.55</v>
@@ -4649,28 +4649,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M41">
-        <v>3.544382400000001</v>
+        <v>3.635264</v>
       </c>
       <c r="N41">
-        <v>5.925617599999998</v>
+        <v>5.834735999999999</v>
       </c>
       <c r="O41">
-        <v>0.5333055839999998</v>
+        <v>0.5251262399999999</v>
       </c>
       <c r="P41">
-        <v>5.392312015999998</v>
+        <v>5.309609759999999</v>
       </c>
       <c r="Q41">
-        <v>7.122312015999999</v>
+        <v>7.039609759999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1209258294746372</v>
+        <v>0.1221066859506437</v>
       </c>
       <c r="T41">
-        <v>1.093172356895145</v>
+        <v>1.110355257450895</v>
       </c>
       <c r="U41">
         <v>0.07190000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.67183360350734</v>
+        <v>2.605037763419658</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09943561157038623</v>
+        <v>0.09958915716124377</v>
       </c>
       <c r="C42">
-        <v>66.10374588556689</v>
+        <v>64.61607343096352</v>
       </c>
       <c r="D42">
-        <v>113.1137458855669</v>
+        <v>112.8900734309635</v>
       </c>
       <c r="E42">
-        <v>50.56</v>
+        <v>51.82400000000001</v>
       </c>
       <c r="F42">
-        <v>50.56</v>
+        <v>51.82400000000001</v>
       </c>
       <c r="G42">
         <v>3.55</v>
@@ -4731,28 +4731,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M42">
-        <v>3.635264</v>
+        <v>3.726145600000001</v>
       </c>
       <c r="N42">
-        <v>5.834735999999999</v>
+        <v>5.743854399999998</v>
       </c>
       <c r="O42">
-        <v>0.5251262399999999</v>
+        <v>0.5169468959999999</v>
       </c>
       <c r="P42">
-        <v>5.309609759999999</v>
+        <v>5.226907503999998</v>
       </c>
       <c r="Q42">
-        <v>7.039609759999999</v>
+        <v>6.956907503999998</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1221066859506437</v>
+        <v>0.1233275714597352</v>
       </c>
       <c r="T42">
-        <v>1.110355257450895</v>
+        <v>1.128120629211925</v>
       </c>
       <c r="U42">
         <v>0.07190000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.605037763419658</v>
+        <v>2.541500256994788</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09958915716124377</v>
+        <v>0.1012332827521013</v>
       </c>
       <c r="C43">
-        <v>64.61607343096352</v>
+        <v>61.01134551836451</v>
       </c>
       <c r="D43">
-        <v>112.8900734309635</v>
+        <v>110.5493455183645</v>
       </c>
       <c r="E43">
-        <v>51.82400000000001</v>
+        <v>53.08800000000001</v>
       </c>
       <c r="F43">
-        <v>51.82400000000001</v>
+        <v>53.08800000000001</v>
       </c>
       <c r="G43">
         <v>3.55</v>
@@ -4813,45 +4813,45 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M43">
-        <v>3.726145600000001</v>
+        <v>4.024070400000001</v>
       </c>
       <c r="N43">
-        <v>5.743854399999998</v>
+        <v>5.445929599999998</v>
       </c>
       <c r="O43">
-        <v>0.5169468959999999</v>
+        <v>0.4901336639999998</v>
       </c>
       <c r="P43">
-        <v>5.226907503999998</v>
+        <v>4.955795935999998</v>
       </c>
       <c r="Q43">
-        <v>6.956907503999998</v>
+        <v>6.685795935999998</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1233275714597352</v>
+        <v>0.1245905564691401</v>
       </c>
       <c r="T43">
-        <v>1.128120629211925</v>
+        <v>1.146498599999196</v>
       </c>
       <c r="U43">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V43">
         <v>0.09</v>
       </c>
       <c r="W43">
-        <v>0.065429</v>
+        <v>0.06897800000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.541500256994788</v>
+        <v>2.353338549941869</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1012332827521013</v>
+        <v>0.1014223183429588</v>
       </c>
       <c r="C44">
-        <v>61.01134551836449</v>
+        <v>59.48442418613034</v>
       </c>
       <c r="D44">
-        <v>110.5493455183645</v>
+        <v>110.2864241861303</v>
       </c>
       <c r="E44">
-        <v>53.088</v>
+        <v>54.352</v>
       </c>
       <c r="F44">
-        <v>53.088</v>
+        <v>54.352</v>
       </c>
       <c r="G44">
         <v>3.55</v>
@@ -4895,28 +4895,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M44">
-        <v>4.0240704</v>
+        <v>4.1198816</v>
       </c>
       <c r="N44">
-        <v>5.445929599999999</v>
+        <v>5.350118399999999</v>
       </c>
       <c r="O44">
-        <v>0.4901336639999999</v>
+        <v>0.4815106559999999</v>
       </c>
       <c r="P44">
-        <v>4.955795935999999</v>
+        <v>4.868607743999998</v>
       </c>
       <c r="Q44">
-        <v>6.685795935999998</v>
+        <v>6.598607743999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1245905564691401</v>
+        <v>0.125897856742033</v>
       </c>
       <c r="T44">
-        <v>1.146498599999196</v>
+        <v>1.165521411866723</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.353338549941869</v>
+        <v>2.298609746454849</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1014223183429588</v>
+        <v>0.1016113539338163</v>
       </c>
       <c r="C45">
-        <v>59.48442418613034</v>
+        <v>57.95875050686654</v>
       </c>
       <c r="D45">
-        <v>110.2864241861303</v>
+        <v>110.0247505068665</v>
       </c>
       <c r="E45">
-        <v>54.352</v>
+        <v>55.616</v>
       </c>
       <c r="F45">
-        <v>54.352</v>
+        <v>55.616</v>
       </c>
       <c r="G45">
         <v>3.55</v>
@@ -4977,28 +4977,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M45">
-        <v>4.1198816</v>
+        <v>4.2156928</v>
       </c>
       <c r="N45">
-        <v>5.350118399999999</v>
+        <v>5.254307199999999</v>
       </c>
       <c r="O45">
-        <v>0.4815106559999999</v>
+        <v>0.4728876479999999</v>
       </c>
       <c r="P45">
-        <v>4.868607743999998</v>
+        <v>4.781419551999999</v>
       </c>
       <c r="Q45">
-        <v>6.598607743999999</v>
+        <v>6.511419552</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.125897856742033</v>
+        <v>0.1272518463103863</v>
       </c>
       <c r="T45">
-        <v>1.165521411866723</v>
+        <v>1.185223609872376</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.298609746454849</v>
+        <v>2.246368615853603</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1016113539338163</v>
+        <v>0.1018003895246739</v>
       </c>
       <c r="C46">
-        <v>57.95875050686654</v>
+        <v>56.43431562077492</v>
       </c>
       <c r="D46">
-        <v>110.0247505068665</v>
+        <v>109.7643156207749</v>
       </c>
       <c r="E46">
-        <v>55.616</v>
+        <v>56.88</v>
       </c>
       <c r="F46">
-        <v>55.616</v>
+        <v>56.88</v>
       </c>
       <c r="G46">
         <v>3.55</v>
@@ -5059,28 +5059,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M46">
-        <v>4.2156928</v>
+        <v>4.311504</v>
       </c>
       <c r="N46">
-        <v>5.254307199999999</v>
+        <v>5.158495999999999</v>
       </c>
       <c r="O46">
-        <v>0.4728876479999999</v>
+        <v>0.4642646399999998</v>
       </c>
       <c r="P46">
-        <v>4.781419551999999</v>
+        <v>4.694231359999999</v>
       </c>
       <c r="Q46">
-        <v>6.511419552</v>
+        <v>6.424231359999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1272518463103863</v>
+        <v>0.1286550718630434</v>
       </c>
       <c r="T46">
-        <v>1.185223609872376</v>
+        <v>1.205642251441871</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.246368615853603</v>
+        <v>2.196449313279078</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1018003895246739</v>
+        <v>0.1019894251155314</v>
       </c>
       <c r="C47">
-        <v>56.43431562077492</v>
+        <v>54.91111075174594</v>
       </c>
       <c r="D47">
-        <v>109.7643156207749</v>
+        <v>109.5051107517459</v>
       </c>
       <c r="E47">
-        <v>56.88</v>
+        <v>58.14400000000001</v>
       </c>
       <c r="F47">
-        <v>56.88</v>
+        <v>58.14400000000001</v>
       </c>
       <c r="G47">
         <v>3.55</v>
@@ -5141,28 +5141,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M47">
-        <v>4.311504</v>
+        <v>4.407315200000001</v>
       </c>
       <c r="N47">
-        <v>5.158495999999999</v>
+        <v>5.062684799999998</v>
       </c>
       <c r="O47">
-        <v>0.4642646399999998</v>
+        <v>0.4556416319999998</v>
       </c>
       <c r="P47">
-        <v>4.694231359999999</v>
+        <v>4.607043167999998</v>
       </c>
       <c r="Q47">
-        <v>6.424231359999999</v>
+        <v>6.337043167999997</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1286550718630434</v>
+        <v>0.1301102687324655</v>
       </c>
       <c r="T47">
-        <v>1.205642251441871</v>
+        <v>1.226817138995422</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.196449313279078</v>
+        <v>2.148700415164315</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1019894251155314</v>
+        <v>0.1021784607063889</v>
       </c>
       <c r="C48">
-        <v>54.91111075174594</v>
+        <v>53.38912720637264</v>
       </c>
       <c r="D48">
-        <v>109.5051107517459</v>
+        <v>109.2471272063727</v>
       </c>
       <c r="E48">
-        <v>58.14400000000001</v>
+        <v>59.40800000000001</v>
       </c>
       <c r="F48">
-        <v>58.14400000000001</v>
+        <v>59.40800000000001</v>
       </c>
       <c r="G48">
         <v>3.55</v>
@@ -5223,28 +5223,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M48">
-        <v>4.407315200000001</v>
+        <v>4.503126400000001</v>
       </c>
       <c r="N48">
-        <v>5.062684799999998</v>
+        <v>4.966873599999998</v>
       </c>
       <c r="O48">
-        <v>0.4556416319999998</v>
+        <v>0.4470186239999998</v>
       </c>
       <c r="P48">
-        <v>4.607043167999998</v>
+        <v>4.519854975999998</v>
       </c>
       <c r="Q48">
-        <v>6.337043167999997</v>
+        <v>6.249854975999998</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1301102687324655</v>
+        <v>0.1316203786912998</v>
       </c>
       <c r="T48">
-        <v>1.226817138995422</v>
+        <v>1.248791078909484</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.148700415164315</v>
+        <v>2.102983385054436</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1021784607063889</v>
+        <v>0.1023674962972464</v>
       </c>
       <c r="C49">
-        <v>53.38912720637264</v>
+        <v>51.86835637297893</v>
       </c>
       <c r="D49">
-        <v>109.2471272063727</v>
+        <v>108.9903563729789</v>
       </c>
       <c r="E49">
-        <v>59.40800000000001</v>
+        <v>60.672</v>
       </c>
       <c r="F49">
-        <v>59.40800000000001</v>
+        <v>60.672</v>
       </c>
       <c r="G49">
         <v>3.55</v>
@@ -5305,28 +5305,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M49">
-        <v>4.503126400000001</v>
+        <v>4.598937600000001</v>
       </c>
       <c r="N49">
-        <v>4.966873599999998</v>
+        <v>4.871062399999998</v>
       </c>
       <c r="O49">
-        <v>0.4470186239999998</v>
+        <v>0.4383956159999998</v>
       </c>
       <c r="P49">
-        <v>4.519854975999998</v>
+        <v>4.432666783999998</v>
       </c>
       <c r="Q49">
-        <v>6.249854975999998</v>
+        <v>6.162666783999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1316203786912998</v>
+        <v>0.133188569802397</v>
       </c>
       <c r="T49">
-        <v>1.248791078909484</v>
+        <v>1.271610170358701</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.102983385054436</v>
+        <v>2.059171231199135</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1023674962972464</v>
+        <v>0.1025565318881039</v>
       </c>
       <c r="C50">
-        <v>51.86835637297894</v>
+        <v>50.34878972066117</v>
       </c>
       <c r="D50">
-        <v>108.9903563729789</v>
+        <v>108.7347897206612</v>
       </c>
       <c r="E50">
-        <v>60.672</v>
+        <v>61.936</v>
       </c>
       <c r="F50">
-        <v>60.672</v>
+        <v>61.936</v>
       </c>
       <c r="G50">
         <v>3.55</v>
@@ -5387,28 +5387,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M50">
-        <v>4.5989376</v>
+        <v>4.6947488</v>
       </c>
       <c r="N50">
-        <v>4.871062399999999</v>
+        <v>4.775251199999999</v>
       </c>
       <c r="O50">
-        <v>0.4383956159999999</v>
+        <v>0.4297726079999999</v>
       </c>
       <c r="P50">
-        <v>4.432666783999998</v>
+        <v>4.345478591999999</v>
       </c>
       <c r="Q50">
-        <v>6.162666783999999</v>
+        <v>6.075478592</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.133188569802397</v>
+        <v>0.1348182586041254</v>
       </c>
       <c r="T50">
-        <v>1.271610170358701</v>
+        <v>1.295324128139261</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.059171231199135</v>
+        <v>2.017147328521602</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1025565318881039</v>
+        <v>0.1092065674789615</v>
       </c>
       <c r="C51">
-        <v>50.34878972066117</v>
+        <v>40.79885525926501</v>
       </c>
       <c r="D51">
-        <v>108.7347897206612</v>
+        <v>100.448855259265</v>
       </c>
       <c r="E51">
-        <v>61.936</v>
+        <v>63.2</v>
       </c>
       <c r="F51">
-        <v>61.936</v>
+        <v>63.2</v>
       </c>
       <c r="G51">
         <v>3.55</v>
@@ -5469,45 +5469,45 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M51">
-        <v>4.6947488</v>
+        <v>5.688</v>
       </c>
       <c r="N51">
-        <v>4.775251199999999</v>
+        <v>3.781999999999999</v>
       </c>
       <c r="O51">
-        <v>0.4297726079999999</v>
+        <v>0.3403799999999999</v>
       </c>
       <c r="P51">
-        <v>4.345478591999999</v>
+        <v>3.441619999999999</v>
       </c>
       <c r="Q51">
-        <v>6.075478592</v>
+        <v>5.171619999999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1348182586041254</v>
+        <v>0.1365131349579229</v>
       </c>
       <c r="T51">
-        <v>1.295324128139261</v>
+        <v>1.319986644231043</v>
       </c>
       <c r="U51">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V51">
         <v>0.09</v>
       </c>
       <c r="W51">
-        <v>0.06897800000000001</v>
+        <v>0.0819</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.017147328521602</v>
+        <v>1.664908579465541</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1092065674789615</v>
+        <v>0.109524823069819</v>
       </c>
       <c r="C52">
-        <v>40.79885525926501</v>
+        <v>39.16985843403229</v>
       </c>
       <c r="D52">
-        <v>100.448855259265</v>
+        <v>100.0838584340323</v>
       </c>
       <c r="E52">
-        <v>63.2</v>
+        <v>64.464</v>
       </c>
       <c r="F52">
-        <v>63.2</v>
+        <v>64.464</v>
       </c>
       <c r="G52">
         <v>3.55</v>
@@ -5551,28 +5551,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M52">
-        <v>5.688</v>
+        <v>5.80176</v>
       </c>
       <c r="N52">
-        <v>3.781999999999999</v>
+        <v>3.668239999999999</v>
       </c>
       <c r="O52">
-        <v>0.3403799999999999</v>
+        <v>0.3301415999999999</v>
       </c>
       <c r="P52">
-        <v>3.441619999999999</v>
+        <v>3.338098399999999</v>
       </c>
       <c r="Q52">
-        <v>5.171619999999999</v>
+        <v>5.068098399999998</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1365131349579229</v>
+        <v>0.1382771899384061</v>
       </c>
       <c r="T52">
-        <v>1.319986644231043</v>
+        <v>1.345655793632694</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.664908579465541</v>
+        <v>1.632263313201511</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.109524823069819</v>
+        <v>0.1098430786606765</v>
       </c>
       <c r="C53">
-        <v>39.16985843403229</v>
+        <v>37.54350455279338</v>
       </c>
       <c r="D53">
-        <v>100.0838584340323</v>
+        <v>99.72150455279339</v>
       </c>
       <c r="E53">
-        <v>64.464</v>
+        <v>65.72800000000001</v>
       </c>
       <c r="F53">
-        <v>64.464</v>
+        <v>65.72800000000001</v>
       </c>
       <c r="G53">
         <v>3.55</v>
@@ -5633,28 +5633,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M53">
-        <v>5.80176</v>
+        <v>5.915520000000001</v>
       </c>
       <c r="N53">
-        <v>3.668239999999999</v>
+        <v>3.554479999999998</v>
       </c>
       <c r="O53">
-        <v>0.3301415999999999</v>
+        <v>0.3199031999999998</v>
       </c>
       <c r="P53">
-        <v>3.338098399999999</v>
+        <v>3.234576799999998</v>
       </c>
       <c r="Q53">
-        <v>5.068098399999998</v>
+        <v>4.964576799999998</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1382771899384061</v>
+        <v>0.1401147472097427</v>
       </c>
       <c r="T53">
-        <v>1.345655793632694</v>
+        <v>1.37239449092608</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.632263313201511</v>
+        <v>1.600873634101482</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1098430786606765</v>
+        <v>0.110161334251534</v>
       </c>
       <c r="C54">
-        <v>37.54350455279338</v>
+        <v>35.91976501274711</v>
       </c>
       <c r="D54">
-        <v>99.72150455279339</v>
+        <v>99.36176501274711</v>
       </c>
       <c r="E54">
-        <v>65.72800000000001</v>
+        <v>66.992</v>
       </c>
       <c r="F54">
-        <v>65.72800000000001</v>
+        <v>66.992</v>
       </c>
       <c r="G54">
         <v>3.55</v>
@@ -5715,28 +5715,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M54">
-        <v>5.915520000000001</v>
+        <v>6.02928</v>
       </c>
       <c r="N54">
-        <v>3.554479999999998</v>
+        <v>3.440719999999999</v>
       </c>
       <c r="O54">
-        <v>0.3199031999999998</v>
+        <v>0.3096647999999999</v>
       </c>
       <c r="P54">
-        <v>3.234576799999998</v>
+        <v>3.131055199999999</v>
       </c>
       <c r="Q54">
-        <v>4.964576799999998</v>
+        <v>4.861055199999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1401147472097427</v>
+        <v>0.1420304984075192</v>
       </c>
       <c r="T54">
-        <v>1.37239449092608</v>
+        <v>1.400271005125568</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.600873634101482</v>
+        <v>1.570668471193907</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.110161334251534</v>
+        <v>0.1104795898423916</v>
       </c>
       <c r="C55">
-        <v>35.91976501274711</v>
+        <v>34.29861162234042</v>
       </c>
       <c r="D55">
-        <v>99.36176501274711</v>
+        <v>99.00461162234043</v>
       </c>
       <c r="E55">
-        <v>66.992</v>
+        <v>68.25600000000001</v>
       </c>
       <c r="F55">
-        <v>66.992</v>
+        <v>68.25600000000001</v>
       </c>
       <c r="G55">
         <v>3.55</v>
@@ -5797,28 +5797,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M55">
-        <v>6.02928</v>
+        <v>6.143040000000001</v>
       </c>
       <c r="N55">
-        <v>3.440719999999999</v>
+        <v>3.326959999999998</v>
       </c>
       <c r="O55">
-        <v>0.3096647999999999</v>
+        <v>0.2994263999999998</v>
       </c>
       <c r="P55">
-        <v>3.131055199999999</v>
+        <v>3.027533599999998</v>
       </c>
       <c r="Q55">
-        <v>4.861055199999999</v>
+        <v>4.757533599999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1420304984075192</v>
+        <v>0.1440295431356338</v>
       </c>
       <c r="T55">
-        <v>1.400271005125568</v>
+        <v>1.429359541681555</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.570668471193907</v>
+        <v>1.541582018023649</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1104795898423916</v>
+        <v>0.1107978454332491</v>
       </c>
       <c r="C56">
-        <v>34.29861162234042</v>
+        <v>32.68001659390404</v>
       </c>
       <c r="D56">
-        <v>99.00461162234043</v>
+        <v>98.65001659390406</v>
       </c>
       <c r="E56">
-        <v>68.25600000000001</v>
+        <v>69.52000000000001</v>
       </c>
       <c r="F56">
-        <v>68.25600000000001</v>
+        <v>69.52000000000001</v>
       </c>
       <c r="G56">
         <v>3.55</v>
@@ -5879,28 +5879,28 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M56">
-        <v>6.143040000000001</v>
+        <v>6.256800000000001</v>
       </c>
       <c r="N56">
-        <v>3.326959999999998</v>
+        <v>3.213199999999998</v>
       </c>
       <c r="O56">
-        <v>0.2994263999999998</v>
+        <v>0.2891879999999998</v>
       </c>
       <c r="P56">
-        <v>3.027533599999998</v>
+        <v>2.924011999999998</v>
       </c>
       <c r="Q56">
-        <v>4.757533599999999</v>
+        <v>4.654011999999998</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1440295431356338</v>
+        <v>0.1461174342961091</v>
       </c>
       <c r="T56">
-        <v>1.429359541681555</v>
+        <v>1.459740902084475</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.541582018023649</v>
+        <v>1.513553254059583</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1107978454332491</v>
+        <v>0.1409294034155801</v>
       </c>
       <c r="C57">
-        <v>32.68001659390404</v>
+        <v>6.435110357596685</v>
       </c>
       <c r="D57">
-        <v>98.65001659390406</v>
+        <v>73.66911035759669</v>
       </c>
       <c r="E57">
-        <v>69.52000000000001</v>
+        <v>70.78400000000001</v>
       </c>
       <c r="F57">
-        <v>69.52000000000001</v>
+        <v>70.78400000000001</v>
       </c>
       <c r="G57">
         <v>3.55</v>
@@ -5961,45 +5961,45 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M57">
-        <v>6.256800000000001</v>
+        <v>10.3910912</v>
       </c>
       <c r="N57">
-        <v>3.213199999999998</v>
+        <v>-0.9210912000000029</v>
       </c>
       <c r="O57">
-        <v>0.2891879999999998</v>
+        <v>-0.08289820800000025</v>
       </c>
       <c r="P57">
-        <v>2.924011999999998</v>
+        <v>-0.8381929920000026</v>
       </c>
       <c r="Q57">
-        <v>4.654011999999998</v>
+        <v>0.8918070079999973</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1461174342961091</v>
+        <v>0.1487824617327625</v>
       </c>
       <c r="T57">
-        <v>1.459740902084475</v>
+        <v>1.498520298524953</v>
       </c>
       <c r="U57">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.09</v>
+        <v>0.08202218454208156</v>
       </c>
       <c r="W57">
-        <v>0.0819</v>
+        <v>0.1347591433092225</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y57">
-        <v>1.513553254059583</v>
+        <v>0.9113576060231284</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1409294034155801</v>
+        <v>0.1419394034155801</v>
       </c>
       <c r="C58">
-        <v>6.435110357596685</v>
+        <v>4.551062148994546</v>
       </c>
       <c r="D58">
-        <v>73.66911035759669</v>
+        <v>73.04906214899457</v>
       </c>
       <c r="E58">
-        <v>70.78400000000001</v>
+        <v>72.04800000000002</v>
       </c>
       <c r="F58">
-        <v>70.78400000000001</v>
+        <v>72.04800000000002</v>
       </c>
       <c r="G58">
         <v>3.55</v>
@@ -6043,37 +6043,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M58">
-        <v>10.3910912</v>
+        <v>10.5766464</v>
       </c>
       <c r="N58">
-        <v>-0.9210912000000029</v>
+        <v>-1.106646400000004</v>
       </c>
       <c r="O58">
-        <v>-0.08289820800000025</v>
+        <v>-0.09959817600000039</v>
       </c>
       <c r="P58">
-        <v>-0.8381929920000026</v>
+        <v>-1.007048224000004</v>
       </c>
       <c r="Q58">
-        <v>0.8918070079999973</v>
+        <v>0.7229517759999962</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1487824617327625</v>
+        <v>0.1511774027032919</v>
       </c>
       <c r="T58">
-        <v>1.498520298524953</v>
+        <v>1.533369607792975</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.08202218454208156</v>
+        <v>0.08058319884836082</v>
       </c>
       <c r="W58">
-        <v>0.1347591433092225</v>
+        <v>0.1349703864090606</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.9113576060231284</v>
+        <v>0.8953688760928981</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1419394034155801</v>
+        <v>0.1429494034155801</v>
       </c>
       <c r="C59">
-        <v>4.551062148994546</v>
+        <v>2.67736430075216</v>
       </c>
       <c r="D59">
-        <v>73.04906214899457</v>
+        <v>72.43936430075217</v>
       </c>
       <c r="E59">
-        <v>72.04800000000002</v>
+        <v>73.31200000000001</v>
       </c>
       <c r="F59">
-        <v>72.04800000000002</v>
+        <v>73.31200000000001</v>
       </c>
       <c r="G59">
         <v>3.55</v>
@@ -6125,37 +6125,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M59">
-        <v>10.5766464</v>
+        <v>10.7622016</v>
       </c>
       <c r="N59">
-        <v>-1.106646400000004</v>
+        <v>-1.292201600000004</v>
       </c>
       <c r="O59">
-        <v>-0.09959817600000039</v>
+        <v>-0.1162981440000003</v>
       </c>
       <c r="P59">
-        <v>-1.007048224000004</v>
+        <v>-1.175903456000003</v>
       </c>
       <c r="Q59">
-        <v>0.7229517759999962</v>
+        <v>0.5540965439999965</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1511774027032919</v>
+        <v>0.1536863884819417</v>
       </c>
       <c r="T59">
-        <v>1.533369607792975</v>
+        <v>1.569878407978522</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.08058319884836082</v>
+        <v>0.07919383335097528</v>
       </c>
       <c r="W59">
-        <v>0.1349703864090606</v>
+        <v>0.1351743452640768</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8953688760928981</v>
+        <v>0.8799314816775032</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1429494034155801</v>
+        <v>0.1439594034155801</v>
       </c>
       <c r="C60">
-        <v>2.677364300752174</v>
+        <v>0.8137597928311635</v>
       </c>
       <c r="D60">
-        <v>72.43936430075217</v>
+        <v>71.83975979283116</v>
       </c>
       <c r="E60">
-        <v>73.312</v>
+        <v>74.57599999999999</v>
       </c>
       <c r="F60">
-        <v>73.312</v>
+        <v>74.57599999999999</v>
       </c>
       <c r="G60">
         <v>3.55</v>
@@ -6207,37 +6207,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M60">
-        <v>10.7622016</v>
+        <v>10.9477568</v>
       </c>
       <c r="N60">
-        <v>-1.292201600000002</v>
+        <v>-1.477756800000002</v>
       </c>
       <c r="O60">
-        <v>-0.1162981440000002</v>
+        <v>-0.1329981120000001</v>
       </c>
       <c r="P60">
-        <v>-1.175903456000002</v>
+        <v>-1.344758688000002</v>
       </c>
       <c r="Q60">
-        <v>0.5540965439999981</v>
+        <v>0.3852413119999984</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1536863884819417</v>
+        <v>0.1563177638107695</v>
       </c>
       <c r="T60">
-        <v>1.569878407978522</v>
+        <v>1.60816812524629</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.07919383335097531</v>
+        <v>0.07785156498909437</v>
       </c>
       <c r="W60">
-        <v>0.1351743452640768</v>
+        <v>0.135371390259601</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8799314816775035</v>
+        <v>0.8650173887677153</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1439594034155801</v>
+        <v>0.1449694034155801</v>
       </c>
       <c r="C61">
-        <v>0.8137597928311635</v>
+        <v>-1.039999954908197</v>
       </c>
       <c r="D61">
-        <v>71.83975979283116</v>
+        <v>71.25000004509181</v>
       </c>
       <c r="E61">
-        <v>74.57599999999999</v>
+        <v>75.84</v>
       </c>
       <c r="F61">
-        <v>74.57599999999999</v>
+        <v>75.84</v>
       </c>
       <c r="G61">
         <v>3.55</v>
@@ -6289,37 +6289,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M61">
-        <v>10.9477568</v>
+        <v>11.133312</v>
       </c>
       <c r="N61">
-        <v>-1.477756800000002</v>
+        <v>-1.663312000000003</v>
       </c>
       <c r="O61">
-        <v>-0.1329981120000001</v>
+        <v>-0.1496980800000003</v>
       </c>
       <c r="P61">
-        <v>-1.344758688000002</v>
+        <v>-1.513613920000003</v>
       </c>
       <c r="Q61">
-        <v>0.3852413119999984</v>
+        <v>0.2163860799999973</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1563177638107695</v>
+        <v>0.1590807079060387</v>
       </c>
       <c r="T61">
-        <v>1.60816812524629</v>
+        <v>1.648372328377448</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.07785156498909437</v>
+        <v>0.07655403890594278</v>
       </c>
       <c r="W61">
-        <v>0.135371390259601</v>
+        <v>0.1355618670886076</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8650173887677153</v>
+        <v>0.8506004322882532</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1449694034155801</v>
+        <v>0.1459794034155801</v>
       </c>
       <c r="C62">
-        <v>-1.039999954908197</v>
+        <v>-2.884155426317676</v>
       </c>
       <c r="D62">
-        <v>71.25000004509181</v>
+        <v>70.66984457368233</v>
       </c>
       <c r="E62">
-        <v>75.84</v>
+        <v>77.104</v>
       </c>
       <c r="F62">
-        <v>75.84</v>
+        <v>77.104</v>
       </c>
       <c r="G62">
         <v>3.55</v>
@@ -6371,37 +6371,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M62">
-        <v>11.133312</v>
+        <v>11.3188672</v>
       </c>
       <c r="N62">
-        <v>-1.663312000000003</v>
+        <v>-1.848867200000003</v>
       </c>
       <c r="O62">
-        <v>-0.1496980800000003</v>
+        <v>-0.1663980480000002</v>
       </c>
       <c r="P62">
-        <v>-1.513613920000003</v>
+        <v>-1.682469152000002</v>
       </c>
       <c r="Q62">
-        <v>0.2163860799999973</v>
+        <v>0.04753084799999763</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1590807079060387</v>
+        <v>0.161985341442091</v>
       </c>
       <c r="T62">
-        <v>1.648372328377448</v>
+        <v>1.690638285515331</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.07655403890594278</v>
+        <v>0.07529905466158307</v>
       </c>
       <c r="W62">
-        <v>0.1355618670886076</v>
+        <v>0.1357460987756796</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8506004322882532</v>
+        <v>0.8366561629064786</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1459794034155801</v>
+        <v>0.1469894034155801</v>
       </c>
       <c r="C63">
-        <v>-2.884155426317676</v>
+        <v>-4.718939335920396</v>
       </c>
       <c r="D63">
-        <v>70.66984457368233</v>
+        <v>70.09906066407962</v>
       </c>
       <c r="E63">
-        <v>77.104</v>
+        <v>78.36800000000001</v>
       </c>
       <c r="F63">
-        <v>77.104</v>
+        <v>78.36800000000001</v>
       </c>
       <c r="G63">
         <v>3.55</v>
@@ -6453,37 +6453,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M63">
-        <v>11.3188672</v>
+        <v>11.5044224</v>
       </c>
       <c r="N63">
-        <v>-1.848867200000003</v>
+        <v>-2.034422400000004</v>
       </c>
       <c r="O63">
-        <v>-0.1663980480000002</v>
+        <v>-0.1830980160000004</v>
       </c>
       <c r="P63">
-        <v>-1.682469152000002</v>
+        <v>-1.851324384000004</v>
       </c>
       <c r="Q63">
-        <v>0.04753084799999763</v>
+        <v>-0.1213243840000036</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.161985341442091</v>
+        <v>0.1650428504274092</v>
       </c>
       <c r="T63">
-        <v>1.690638285515331</v>
+        <v>1.735128766713103</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.07529905466158307</v>
+        <v>0.07408455377994462</v>
       </c>
       <c r="W63">
-        <v>0.1357460987756796</v>
+        <v>0.1359243875051041</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8366561629064786</v>
+        <v>0.8231617086660514</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1469894034155801</v>
+        <v>0.1479994034155801</v>
       </c>
       <c r="C64">
-        <v>-4.718939335920396</v>
+        <v>-6.544576940152211</v>
       </c>
       <c r="D64">
-        <v>70.09906066407962</v>
+        <v>69.5374230598478</v>
       </c>
       <c r="E64">
-        <v>78.36800000000001</v>
+        <v>79.63200000000001</v>
       </c>
       <c r="F64">
-        <v>78.36800000000001</v>
+        <v>79.63200000000001</v>
       </c>
       <c r="G64">
         <v>3.55</v>
@@ -6535,37 +6535,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M64">
-        <v>11.5044224</v>
+        <v>11.6899776</v>
       </c>
       <c r="N64">
-        <v>-2.034422400000004</v>
+        <v>-2.219977600000004</v>
       </c>
       <c r="O64">
-        <v>-0.1830980160000004</v>
+        <v>-0.1997979840000003</v>
       </c>
       <c r="P64">
-        <v>-1.851324384000004</v>
+        <v>-2.020179616000003</v>
       </c>
       <c r="Q64">
-        <v>-0.1213243840000036</v>
+        <v>-0.2901796160000032</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1650428504274092</v>
+        <v>0.1682656301686906</v>
       </c>
       <c r="T64">
-        <v>1.735128766713103</v>
+        <v>1.78202413878643</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.07408455377994462</v>
+        <v>0.07290860848185027</v>
       </c>
       <c r="W64">
-        <v>0.1359243875051041</v>
+        <v>0.1360970162748644</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8231617086660514</v>
+        <v>0.8100956497983364</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1479994034155801</v>
+        <v>0.1841560630658698</v>
       </c>
       <c r="C65">
-        <v>-6.544576940152211</v>
+        <v>-23.30785138755856</v>
       </c>
       <c r="D65">
-        <v>69.5374230598478</v>
+        <v>54.03814861244145</v>
       </c>
       <c r="E65">
-        <v>79.63200000000001</v>
+        <v>80.896</v>
       </c>
       <c r="F65">
-        <v>79.63200000000001</v>
+        <v>80.896</v>
       </c>
       <c r="G65">
         <v>3.55</v>
@@ -6617,45 +6617,45 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M65">
-        <v>11.6899776</v>
+        <v>16.2439168</v>
       </c>
       <c r="N65">
-        <v>-2.219977600000004</v>
+        <v>-6.773916800000002</v>
       </c>
       <c r="O65">
-        <v>-0.1997979840000003</v>
+        <v>-0.6096525120000001</v>
       </c>
       <c r="P65">
-        <v>-2.020179616000003</v>
+        <v>-6.164264288000002</v>
       </c>
       <c r="Q65">
-        <v>-0.2901796160000032</v>
+        <v>-4.434264288000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1682656301686906</v>
+        <v>0.1732970633686255</v>
       </c>
       <c r="T65">
-        <v>1.78202413878643</v>
+        <v>1.855237622460382</v>
       </c>
       <c r="U65">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.07290860848185027</v>
+        <v>0.05246887253202379</v>
       </c>
       <c r="W65">
-        <v>0.1360970162748644</v>
+        <v>0.1902642503955696</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.8100956497983364</v>
+        <v>0.5829874725780422</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1841560630658698</v>
+        <v>0.1857060630658697</v>
       </c>
       <c r="C66">
-        <v>-23.30785138755856</v>
+        <v>-25.0833054098642</v>
       </c>
       <c r="D66">
-        <v>54.03814861244145</v>
+        <v>53.52669459013582</v>
       </c>
       <c r="E66">
-        <v>80.896</v>
+        <v>82.16000000000001</v>
       </c>
       <c r="F66">
-        <v>80.896</v>
+        <v>82.16000000000001</v>
       </c>
       <c r="G66">
         <v>3.55</v>
@@ -6699,37 +6699,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M66">
-        <v>16.2439168</v>
+        <v>16.497728</v>
       </c>
       <c r="N66">
-        <v>-6.773916800000002</v>
+        <v>-7.027728000000003</v>
       </c>
       <c r="O66">
-        <v>-0.6096525120000001</v>
+        <v>-0.6324955200000003</v>
       </c>
       <c r="P66">
-        <v>-6.164264288000002</v>
+        <v>-6.395232480000003</v>
       </c>
       <c r="Q66">
-        <v>-4.434264288000001</v>
+        <v>-4.665232480000004</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1732970633686255</v>
+        <v>0.1769398366077291</v>
       </c>
       <c r="T66">
-        <v>1.855237622460382</v>
+        <v>1.908244411673535</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.05246887253202379</v>
+        <v>0.0516616591084542</v>
       </c>
       <c r="W66">
-        <v>0.1902642503955696</v>
+        <v>0.1904263388510224</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5829874725780422</v>
+        <v>0.5740184345383799</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1857060630658697</v>
+        <v>0.1872560630658698</v>
       </c>
       <c r="C67">
-        <v>-25.0833054098642</v>
+        <v>-26.84916870357429</v>
       </c>
       <c r="D67">
-        <v>53.52669459013582</v>
+        <v>53.02483129642572</v>
       </c>
       <c r="E67">
-        <v>82.16000000000001</v>
+        <v>83.42400000000001</v>
       </c>
       <c r="F67">
-        <v>82.16000000000001</v>
+        <v>83.42400000000001</v>
       </c>
       <c r="G67">
         <v>3.55</v>
@@ -6781,37 +6781,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M67">
-        <v>16.497728</v>
+        <v>16.7515392</v>
       </c>
       <c r="N67">
-        <v>-7.027728000000003</v>
+        <v>-7.281539200000005</v>
       </c>
       <c r="O67">
-        <v>-0.6324955200000003</v>
+        <v>-0.6553385280000004</v>
       </c>
       <c r="P67">
-        <v>-6.395232480000003</v>
+        <v>-6.626200672000004</v>
       </c>
       <c r="Q67">
-        <v>-4.665232480000004</v>
+        <v>-4.896200672000004</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1769398366077291</v>
+        <v>0.1807968906256035</v>
       </c>
       <c r="T67">
-        <v>1.908244411673535</v>
+        <v>1.964369247310993</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.0516616591084542</v>
+        <v>0.05087890669772003</v>
       </c>
       <c r="W67">
-        <v>0.1904263388510224</v>
+        <v>0.1905835155350978</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5740184345383799</v>
+        <v>0.5653211855302226</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1872560630658698</v>
+        <v>0.1888060630658697</v>
       </c>
       <c r="C68">
-        <v>-26.84916870357429</v>
+        <v>-28.60570852927268</v>
       </c>
       <c r="D68">
-        <v>53.02483129642572</v>
+        <v>52.53229147072732</v>
       </c>
       <c r="E68">
-        <v>83.42400000000001</v>
+        <v>84.688</v>
       </c>
       <c r="F68">
-        <v>83.42400000000001</v>
+        <v>84.688</v>
       </c>
       <c r="G68">
         <v>3.55</v>
@@ -6863,37 +6863,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M68">
-        <v>16.7515392</v>
+        <v>17.0053504</v>
       </c>
       <c r="N68">
-        <v>-7.281539200000005</v>
+        <v>-7.535350400000002</v>
       </c>
       <c r="O68">
-        <v>-0.6553385280000004</v>
+        <v>-0.6781815360000002</v>
       </c>
       <c r="P68">
-        <v>-6.626200672000004</v>
+        <v>-6.857168864000002</v>
       </c>
       <c r="Q68">
-        <v>-4.896200672000004</v>
+        <v>-5.127168864000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1807968906256035</v>
+        <v>0.184887705493046</v>
       </c>
       <c r="T68">
-        <v>1.964369247310993</v>
+        <v>2.023895588138598</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.05087890669772003</v>
+        <v>0.05011952003058989</v>
       </c>
       <c r="W68">
-        <v>0.1905835155350978</v>
+        <v>0.1907360003778575</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5653211855302226</v>
+        <v>0.5568835558954432</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1888060630658697</v>
+        <v>0.1903560630658698</v>
       </c>
       <c r="C69">
-        <v>-28.60570852927268</v>
+        <v>-30.35318230875799</v>
       </c>
       <c r="D69">
-        <v>52.53229147072732</v>
+        <v>52.04881769124202</v>
       </c>
       <c r="E69">
-        <v>84.688</v>
+        <v>85.95200000000001</v>
       </c>
       <c r="F69">
-        <v>84.688</v>
+        <v>85.95200000000001</v>
       </c>
       <c r="G69">
         <v>3.55</v>
@@ -6945,37 +6945,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M69">
-        <v>17.0053504</v>
+        <v>17.2591616</v>
       </c>
       <c r="N69">
-        <v>-7.535350400000002</v>
+        <v>-7.789161600000003</v>
       </c>
       <c r="O69">
-        <v>-0.6781815360000002</v>
+        <v>-0.7010245440000002</v>
       </c>
       <c r="P69">
-        <v>-6.857168864000002</v>
+        <v>-7.088137056000003</v>
       </c>
       <c r="Q69">
-        <v>-5.127168864000001</v>
+        <v>-5.358137056000004</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.184887705493046</v>
+        <v>0.1892341962897038</v>
       </c>
       <c r="T69">
-        <v>2.023895588138598</v>
+        <v>2.08714232526793</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.05011952003058989</v>
+        <v>0.04938246826543416</v>
       </c>
       <c r="W69">
-        <v>0.1907360003778575</v>
+        <v>0.1908840003723008</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5568835558954432</v>
+        <v>0.5486940918381573</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1903560630658698</v>
+        <v>0.1919060630658698</v>
       </c>
       <c r="C70">
-        <v>-30.35318230875799</v>
+        <v>-32.09183807366415</v>
       </c>
       <c r="D70">
-        <v>52.04881769124202</v>
+        <v>51.57416192633586</v>
       </c>
       <c r="E70">
-        <v>85.95200000000001</v>
+        <v>87.21600000000001</v>
       </c>
       <c r="F70">
-        <v>85.95200000000001</v>
+        <v>87.21600000000001</v>
       </c>
       <c r="G70">
         <v>3.55</v>
@@ -7027,37 +7027,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M70">
-        <v>17.2591616</v>
+        <v>17.5129728</v>
       </c>
       <c r="N70">
-        <v>-7.789161600000003</v>
+        <v>-8.042972800000005</v>
       </c>
       <c r="O70">
-        <v>-0.7010245440000002</v>
+        <v>-0.7238675520000004</v>
       </c>
       <c r="P70">
-        <v>-7.088137056000003</v>
+        <v>-7.319105248000004</v>
       </c>
       <c r="Q70">
-        <v>-5.358137056000004</v>
+        <v>-5.589105248000005</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1892341962897038</v>
+        <v>0.1938611058474361</v>
       </c>
       <c r="T70">
-        <v>2.08714232526793</v>
+        <v>2.154469497050766</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.04938246826543416</v>
+        <v>0.0486667803195583</v>
       </c>
       <c r="W70">
-        <v>0.1908840003723008</v>
+        <v>0.1910277105118327</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5486940918381573</v>
+        <v>0.5407420035506477</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1919060630658698</v>
+        <v>0.1934560630658698</v>
       </c>
       <c r="C71">
-        <v>-32.09183807366415</v>
+        <v>-33.82191488975626</v>
       </c>
       <c r="D71">
-        <v>51.57416192633586</v>
+        <v>51.10808511024376</v>
       </c>
       <c r="E71">
-        <v>87.21600000000001</v>
+        <v>88.48000000000002</v>
       </c>
       <c r="F71">
-        <v>87.21600000000001</v>
+        <v>88.48000000000002</v>
       </c>
       <c r="G71">
         <v>3.55</v>
@@ -7109,37 +7109,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M71">
-        <v>17.5129728</v>
+        <v>17.766784</v>
       </c>
       <c r="N71">
-        <v>-8.042972800000005</v>
+        <v>-8.296784000000006</v>
       </c>
       <c r="O71">
-        <v>-0.7238675520000004</v>
+        <v>-0.7467105600000005</v>
       </c>
       <c r="P71">
-        <v>-7.319105248000004</v>
+        <v>-7.550073440000006</v>
       </c>
       <c r="Q71">
-        <v>-5.589105248000005</v>
+        <v>-5.820073440000005</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1938611058474361</v>
+        <v>0.1987964760423507</v>
       </c>
       <c r="T71">
-        <v>2.154469497050766</v>
+        <v>2.226285146952458</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.0486667803195583</v>
+        <v>0.04797154060070746</v>
       </c>
       <c r="W71">
-        <v>0.1910277105118327</v>
+        <v>0.191167314647378</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5407420035506477</v>
+        <v>0.5330171177856384</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1934560630658698</v>
+        <v>0.1950060630658698</v>
       </c>
       <c r="C72">
-        <v>-33.82191488975626</v>
+        <v>-35.54364325842584</v>
       </c>
       <c r="D72">
-        <v>51.10808511024376</v>
+        <v>50.65035674157418</v>
       </c>
       <c r="E72">
-        <v>88.48000000000002</v>
+        <v>89.74400000000001</v>
       </c>
       <c r="F72">
-        <v>88.48000000000002</v>
+        <v>89.74400000000001</v>
       </c>
       <c r="G72">
         <v>3.55</v>
@@ -7191,37 +7191,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M72">
-        <v>17.766784</v>
+        <v>18.0205952</v>
       </c>
       <c r="N72">
-        <v>-8.296784000000006</v>
+        <v>-8.550595200000004</v>
       </c>
       <c r="O72">
-        <v>-0.7467105600000005</v>
+        <v>-0.7695535680000003</v>
       </c>
       <c r="P72">
-        <v>-7.550073440000006</v>
+        <v>-7.781041632000004</v>
       </c>
       <c r="Q72">
-        <v>-5.820073440000005</v>
+        <v>-6.051041632000004</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1987964760423507</v>
+        <v>0.2040722165955352</v>
       </c>
       <c r="T72">
-        <v>2.226285146952458</v>
+        <v>2.303053600295647</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.04797154060070746</v>
+        <v>0.04729588509928905</v>
       </c>
       <c r="W72">
-        <v>0.191167314647378</v>
+        <v>0.1913029862720628</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5330171177856384</v>
+        <v>0.525509834436545</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1950060630658698</v>
+        <v>0.1965560630658698</v>
       </c>
       <c r="C73">
-        <v>-35.54364325842581</v>
+        <v>-37.25724549680285</v>
       </c>
       <c r="D73">
-        <v>50.65035674157419</v>
+        <v>50.20075450319715</v>
       </c>
       <c r="E73">
-        <v>89.744</v>
+        <v>91.008</v>
       </c>
       <c r="F73">
-        <v>89.744</v>
+        <v>91.008</v>
       </c>
       <c r="G73">
         <v>3.55</v>
@@ -7273,37 +7273,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M73">
-        <v>18.0205952</v>
+        <v>18.2744064</v>
       </c>
       <c r="N73">
-        <v>-8.5505952</v>
+        <v>-8.804406400000001</v>
       </c>
       <c r="O73">
-        <v>-0.769553568</v>
+        <v>-0.7923965760000001</v>
       </c>
       <c r="P73">
-        <v>-7.781041632</v>
+        <v>-8.012009824000002</v>
       </c>
       <c r="Q73">
-        <v>-6.051041632</v>
+        <v>-6.282009824000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2040722165955351</v>
+        <v>0.2097247957596614</v>
       </c>
       <c r="T73">
-        <v>2.303053600295646</v>
+        <v>2.385305514591919</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.04729588509928906</v>
+        <v>0.04663899780624338</v>
       </c>
       <c r="W73">
-        <v>0.1913029862720628</v>
+        <v>0.1914348892405063</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5255098344365451</v>
+        <v>0.5182110867360374</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1965560630658698</v>
+        <v>0.1981060630658698</v>
       </c>
       <c r="C74">
-        <v>-37.25724549680285</v>
+        <v>-38.96293609780137</v>
       </c>
       <c r="D74">
-        <v>50.20075450319715</v>
+        <v>49.75906390219864</v>
       </c>
       <c r="E74">
-        <v>91.008</v>
+        <v>92.27200000000001</v>
       </c>
       <c r="F74">
-        <v>91.008</v>
+        <v>92.27200000000001</v>
       </c>
       <c r="G74">
         <v>3.55</v>
@@ -7355,37 +7355,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M74">
-        <v>18.2744064</v>
+        <v>18.5282176</v>
       </c>
       <c r="N74">
-        <v>-8.804406400000001</v>
+        <v>-9.058217600000003</v>
       </c>
       <c r="O74">
-        <v>-0.7923965760000001</v>
+        <v>-0.8152395840000002</v>
       </c>
       <c r="P74">
-        <v>-8.012009824000002</v>
+        <v>-8.242978016000002</v>
       </c>
       <c r="Q74">
-        <v>-6.282009824000001</v>
+        <v>-6.512978016000002</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2097247957596614</v>
+        <v>0.2157960844915007</v>
       </c>
       <c r="T74">
-        <v>2.385305514591919</v>
+        <v>2.473650163280509</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.04663899780624338</v>
+        <v>0.04600010742533593</v>
       </c>
       <c r="W74">
-        <v>0.1914348892405063</v>
+        <v>0.1915631784289926</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5182110867360374</v>
+        <v>0.5111123047259547</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1981060630658698</v>
+        <v>0.1996560630658697</v>
       </c>
       <c r="C75">
-        <v>-38.96293609780137</v>
+        <v>-40.66092207132348</v>
       </c>
       <c r="D75">
-        <v>49.75906390219864</v>
+        <v>49.32507792867653</v>
       </c>
       <c r="E75">
-        <v>92.27200000000001</v>
+        <v>93.536</v>
       </c>
       <c r="F75">
-        <v>92.27200000000001</v>
+        <v>93.536</v>
       </c>
       <c r="G75">
         <v>3.55</v>
@@ -7437,37 +7437,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M75">
-        <v>18.5282176</v>
+        <v>18.7820288</v>
       </c>
       <c r="N75">
-        <v>-9.058217600000003</v>
+        <v>-9.312028800000004</v>
       </c>
       <c r="O75">
-        <v>-0.8152395840000002</v>
+        <v>-0.8380825920000003</v>
       </c>
       <c r="P75">
-        <v>-8.242978016000002</v>
+        <v>-8.473946208000003</v>
       </c>
       <c r="Q75">
-        <v>-6.512978016000002</v>
+        <v>-6.743946208000002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2157960844915007</v>
+        <v>0.2223343954334815</v>
       </c>
       <c r="T75">
-        <v>2.473650163280509</v>
+        <v>2.568790554175913</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.04600010742533593</v>
+        <v>0.04537848435202058</v>
       </c>
       <c r="W75">
-        <v>0.1915631784289926</v>
+        <v>0.1916880003421143</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5111123047259547</v>
+        <v>0.5042053816891174</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1996560630658697</v>
+        <v>0.2276927873208244</v>
       </c>
       <c r="C76">
-        <v>-40.66092207132348</v>
+        <v>-48.64614047563719</v>
       </c>
       <c r="D76">
-        <v>49.32507792867653</v>
+        <v>42.60385952436283</v>
       </c>
       <c r="E76">
-        <v>93.536</v>
+        <v>94.80000000000001</v>
       </c>
       <c r="F76">
-        <v>93.536</v>
+        <v>94.80000000000001</v>
       </c>
       <c r="G76">
         <v>3.55</v>
@@ -7519,45 +7519,45 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M76">
-        <v>18.7820288</v>
+        <v>22.35384000000001</v>
       </c>
       <c r="N76">
-        <v>-9.312028800000004</v>
+        <v>-12.88384000000001</v>
       </c>
       <c r="O76">
-        <v>-0.8380825920000003</v>
+        <v>-1.159545600000001</v>
       </c>
       <c r="P76">
-        <v>-8.473946208000003</v>
+        <v>-11.72429440000001</v>
       </c>
       <c r="Q76">
-        <v>-6.743946208000002</v>
+        <v>-9.994294400000005</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2223343954334815</v>
+        <v>0.2303426682706393</v>
       </c>
       <c r="T76">
-        <v>2.568790554175913</v>
+        <v>2.685320681740238</v>
       </c>
       <c r="U76">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.04537848435202058</v>
+        <v>0.03812767739234063</v>
       </c>
       <c r="W76">
-        <v>0.1916880003421143</v>
+        <v>0.2268094936708861</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.5042053816891174</v>
+        <v>0.4236408599148959</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2276927873208244</v>
+        <v>0.2295927873208244</v>
       </c>
       <c r="C77">
-        <v>-48.64614047563719</v>
+        <v>-50.29995990089875</v>
       </c>
       <c r="D77">
-        <v>42.60385952436283</v>
+        <v>42.21404009910126</v>
       </c>
       <c r="E77">
-        <v>94.80000000000001</v>
+        <v>96.06400000000001</v>
       </c>
       <c r="F77">
-        <v>94.80000000000001</v>
+        <v>96.06400000000001</v>
       </c>
       <c r="G77">
         <v>3.55</v>
@@ -7601,37 +7601,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M77">
-        <v>22.35384000000001</v>
+        <v>22.6518912</v>
       </c>
       <c r="N77">
-        <v>-12.88384000000001</v>
+        <v>-13.1818912</v>
       </c>
       <c r="O77">
-        <v>-1.159545600000001</v>
+        <v>-1.186370208</v>
       </c>
       <c r="P77">
-        <v>-11.72429440000001</v>
+        <v>-11.995520992</v>
       </c>
       <c r="Q77">
-        <v>-9.994294400000005</v>
+        <v>-10.265520992</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2303426682706393</v>
+        <v>0.2380319461152493</v>
       </c>
       <c r="T77">
-        <v>2.685320681740238</v>
+        <v>2.797209043479415</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03812767739234063</v>
+        <v>0.03762599742665194</v>
       </c>
       <c r="W77">
-        <v>0.2268094936708861</v>
+        <v>0.2269277898067955</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4236408599148959</v>
+        <v>0.4180666380739105</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2295927873208244</v>
+        <v>0.2314927873208244</v>
       </c>
       <c r="C78">
-        <v>-50.29995990089875</v>
+        <v>-51.94671041798478</v>
       </c>
       <c r="D78">
-        <v>42.21404009910126</v>
+        <v>41.83128958201523</v>
       </c>
       <c r="E78">
-        <v>96.06400000000001</v>
+        <v>97.328</v>
       </c>
       <c r="F78">
-        <v>96.06400000000001</v>
+        <v>97.328</v>
       </c>
       <c r="G78">
         <v>3.55</v>
@@ -7683,37 +7683,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M78">
-        <v>22.6518912</v>
+        <v>22.9499424</v>
       </c>
       <c r="N78">
-        <v>-13.1818912</v>
+        <v>-13.4799424</v>
       </c>
       <c r="O78">
-        <v>-1.186370208</v>
+        <v>-1.213194816</v>
       </c>
       <c r="P78">
-        <v>-11.995520992</v>
+        <v>-12.266747584</v>
       </c>
       <c r="Q78">
-        <v>-10.265520992</v>
+        <v>-10.536747584</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2380319461152493</v>
+        <v>0.2463898568159123</v>
       </c>
       <c r="T78">
-        <v>2.797209043479415</v>
+        <v>2.91882682797852</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03762599742665194</v>
+        <v>0.0371373481094227</v>
       </c>
       <c r="W78">
-        <v>0.2269277898067955</v>
+        <v>0.2270430133157981</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4180666380739105</v>
+        <v>0.4126372012158078</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2314927873208244</v>
+        <v>0.2333927873208244</v>
       </c>
       <c r="C79">
-        <v>-51.94671041798478</v>
+        <v>-53.58658257845237</v>
       </c>
       <c r="D79">
-        <v>41.83128958201523</v>
+        <v>41.45541742154764</v>
       </c>
       <c r="E79">
-        <v>97.328</v>
+        <v>98.59200000000001</v>
       </c>
       <c r="F79">
-        <v>97.328</v>
+        <v>98.59200000000001</v>
       </c>
       <c r="G79">
         <v>3.55</v>
@@ -7765,37 +7765,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M79">
-        <v>22.9499424</v>
+        <v>23.2479936</v>
       </c>
       <c r="N79">
-        <v>-13.4799424</v>
+        <v>-13.77799360000001</v>
       </c>
       <c r="O79">
-        <v>-1.213194816</v>
+        <v>-1.240019424</v>
       </c>
       <c r="P79">
-        <v>-12.266747584</v>
+        <v>-12.53797417600001</v>
       </c>
       <c r="Q79">
-        <v>-10.536747584</v>
+        <v>-10.80797417600001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2463898568159123</v>
+        <v>0.2555075775802719</v>
       </c>
       <c r="T79">
-        <v>2.91882682797852</v>
+        <v>3.051500774704816</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.0371373481094227</v>
+        <v>0.03666122826186599</v>
       </c>
       <c r="W79">
-        <v>0.2270430133157981</v>
+        <v>0.227155282375852</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4126372012158078</v>
+        <v>0.4073469806873999</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2333927873208244</v>
+        <v>0.2352927873208244</v>
       </c>
       <c r="C80">
-        <v>-53.58658257845237</v>
+        <v>-55.21976014609818</v>
       </c>
       <c r="D80">
-        <v>41.45541742154764</v>
+        <v>41.08623985390183</v>
       </c>
       <c r="E80">
-        <v>98.59200000000001</v>
+        <v>99.85600000000001</v>
       </c>
       <c r="F80">
-        <v>98.59200000000001</v>
+        <v>99.85600000000001</v>
       </c>
       <c r="G80">
         <v>3.55</v>
@@ -7847,37 +7847,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M80">
-        <v>23.2479936</v>
+        <v>23.5460448</v>
       </c>
       <c r="N80">
-        <v>-13.77799360000001</v>
+        <v>-14.07604480000001</v>
       </c>
       <c r="O80">
-        <v>-1.240019424</v>
+        <v>-1.266844032000001</v>
       </c>
       <c r="P80">
-        <v>-12.53797417600001</v>
+        <v>-12.80920076800001</v>
       </c>
       <c r="Q80">
-        <v>-10.80797417600001</v>
+        <v>-11.07920076800001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2555075775802719</v>
+        <v>0.2654936527031421</v>
       </c>
       <c r="T80">
-        <v>3.051500774704816</v>
+        <v>3.196810335405046</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03666122826186599</v>
+        <v>0.03619716208133605</v>
       </c>
       <c r="W80">
-        <v>0.227155282375852</v>
+        <v>0.227264709181221</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4073469806873999</v>
+        <v>0.4021906897926227</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2352927873208244</v>
+        <v>0.2371927873208244</v>
       </c>
       <c r="C81">
-        <v>-55.21976014609818</v>
+        <v>-56.84642039652964</v>
       </c>
       <c r="D81">
-        <v>41.08623985390183</v>
+        <v>40.72357960347037</v>
       </c>
       <c r="E81">
-        <v>99.85600000000001</v>
+        <v>101.12</v>
       </c>
       <c r="F81">
-        <v>99.85600000000001</v>
+        <v>101.12</v>
       </c>
       <c r="G81">
         <v>3.55</v>
@@ -7929,37 +7929,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M81">
-        <v>23.5460448</v>
+        <v>23.844096</v>
       </c>
       <c r="N81">
-        <v>-14.07604480000001</v>
+        <v>-14.374096</v>
       </c>
       <c r="O81">
-        <v>-1.266844032000001</v>
+        <v>-1.29366864</v>
       </c>
       <c r="P81">
-        <v>-12.80920076800001</v>
+        <v>-13.08042736</v>
       </c>
       <c r="Q81">
-        <v>-11.07920076800001</v>
+        <v>-11.35042736</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2654936527031421</v>
+        <v>0.2764783353382992</v>
       </c>
       <c r="T81">
-        <v>3.196810335405046</v>
+        <v>3.356650852175298</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03619716208133605</v>
+        <v>0.03574469755531935</v>
       </c>
       <c r="W81">
-        <v>0.227264709181221</v>
+        <v>0.2273714003164557</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4021906897926227</v>
+        <v>0.397163306170215</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2371927873208244</v>
+        <v>0.2390927873208244</v>
       </c>
       <c r="C82">
-        <v>-56.84642039652964</v>
+        <v>-58.46673440100951</v>
       </c>
       <c r="D82">
-        <v>40.72357960347037</v>
+        <v>40.36726559899051</v>
       </c>
       <c r="E82">
-        <v>101.12</v>
+        <v>102.384</v>
       </c>
       <c r="F82">
-        <v>101.12</v>
+        <v>102.384</v>
       </c>
       <c r="G82">
         <v>3.55</v>
@@ -8011,37 +8011,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M82">
-        <v>23.844096</v>
+        <v>24.1421472</v>
       </c>
       <c r="N82">
-        <v>-14.374096</v>
+        <v>-14.6721472</v>
       </c>
       <c r="O82">
-        <v>-1.29366864</v>
+        <v>-1.320493248</v>
       </c>
       <c r="P82">
-        <v>-13.08042736</v>
+        <v>-13.351653952</v>
       </c>
       <c r="Q82">
-        <v>-11.35042736</v>
+        <v>-11.621653952</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2764783353382992</v>
+        <v>0.2886193003561044</v>
       </c>
       <c r="T82">
-        <v>3.356650852175298</v>
+        <v>3.533316686500314</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03574469755531935</v>
+        <v>0.035303404992908</v>
       </c>
       <c r="W82">
-        <v>0.2273714003164557</v>
+        <v>0.2274754571026723</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.397163306170215</v>
+        <v>0.3922600554767555</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2390927873208244</v>
+        <v>0.2409927873208244</v>
       </c>
       <c r="C83">
-        <v>-58.46673440100951</v>
+        <v>-60.08086729552836</v>
       </c>
       <c r="D83">
-        <v>40.36726559899051</v>
+        <v>40.01713270447165</v>
       </c>
       <c r="E83">
-        <v>102.384</v>
+        <v>103.648</v>
       </c>
       <c r="F83">
-        <v>102.384</v>
+        <v>103.648</v>
       </c>
       <c r="G83">
         <v>3.55</v>
@@ -8093,37 +8093,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M83">
-        <v>24.1421472</v>
+        <v>24.4401984</v>
       </c>
       <c r="N83">
-        <v>-14.6721472</v>
+        <v>-14.9701984</v>
       </c>
       <c r="O83">
-        <v>-1.320493248</v>
+        <v>-1.347317856</v>
       </c>
       <c r="P83">
-        <v>-13.351653952</v>
+        <v>-13.622880544</v>
       </c>
       <c r="Q83">
-        <v>-11.621653952</v>
+        <v>-11.892880544</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2886193003561044</v>
+        <v>0.3021092614869991</v>
       </c>
       <c r="T83">
-        <v>3.533316686500314</v>
+        <v>3.729612057972553</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.035303404992908</v>
+        <v>0.03487287566372619</v>
       </c>
       <c r="W83">
-        <v>0.2274754571026723</v>
+        <v>0.2275769759184934</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3922600554767555</v>
+        <v>0.3874763962636243</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2409927873208244</v>
+        <v>0.2428927873208244</v>
       </c>
       <c r="C84">
-        <v>-60.08086729552836</v>
+        <v>-61.68897853599466</v>
       </c>
       <c r="D84">
-        <v>40.01713270447165</v>
+        <v>39.67302146400536</v>
       </c>
       <c r="E84">
-        <v>103.648</v>
+        <v>104.912</v>
       </c>
       <c r="F84">
-        <v>103.648</v>
+        <v>104.912</v>
       </c>
       <c r="G84">
         <v>3.55</v>
@@ -8175,37 +8175,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M84">
-        <v>24.4401984</v>
+        <v>24.73824960000001</v>
       </c>
       <c r="N84">
-        <v>-14.9701984</v>
+        <v>-15.26824960000001</v>
       </c>
       <c r="O84">
-        <v>-1.347317856</v>
+        <v>-1.374142464000001</v>
       </c>
       <c r="P84">
-        <v>-13.622880544</v>
+        <v>-13.89410713600001</v>
       </c>
       <c r="Q84">
-        <v>-11.892880544</v>
+        <v>-12.16410713600001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3021092614869991</v>
+        <v>0.3171862768685874</v>
       </c>
       <c r="T84">
-        <v>3.729612057972553</v>
+        <v>3.949001002559175</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03487287566372619</v>
+        <v>0.03445272053524756</v>
       </c>
       <c r="W84">
-        <v>0.2275769759184934</v>
+        <v>0.2276760484977886</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3874763962636243</v>
+        <v>0.3828080059471951</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2428927873208244</v>
+        <v>0.2447927873208244</v>
       </c>
       <c r="C85">
-        <v>-61.68897853599466</v>
+        <v>-63.29122214037042</v>
       </c>
       <c r="D85">
-        <v>39.67302146400536</v>
+        <v>39.3347778596296</v>
       </c>
       <c r="E85">
-        <v>104.912</v>
+        <v>106.176</v>
       </c>
       <c r="F85">
-        <v>104.912</v>
+        <v>106.176</v>
       </c>
       <c r="G85">
         <v>3.55</v>
@@ -8257,37 +8257,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M85">
-        <v>24.73824960000001</v>
+        <v>25.03630080000001</v>
       </c>
       <c r="N85">
-        <v>-15.26824960000001</v>
+        <v>-15.56630080000001</v>
       </c>
       <c r="O85">
-        <v>-1.374142464000001</v>
+        <v>-1.400967072000001</v>
       </c>
       <c r="P85">
-        <v>-13.89410713600001</v>
+        <v>-14.16533372800001</v>
       </c>
       <c r="Q85">
-        <v>-12.16410713600001</v>
+        <v>-12.43533372800001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3171862768685874</v>
+        <v>0.3341479191728741</v>
       </c>
       <c r="T85">
-        <v>3.949001002559175</v>
+        <v>4.195813565219124</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03445272053524756</v>
+        <v>0.03404256910030413</v>
       </c>
       <c r="W85">
-        <v>0.2276760484977886</v>
+        <v>0.2277727622061483</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3828080059471951</v>
+        <v>0.3782507677811571</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2447927873208244</v>
+        <v>0.2466927873208244</v>
       </c>
       <c r="C86">
-        <v>-63.29122214037039</v>
+        <v>-64.88774691852529</v>
       </c>
       <c r="D86">
-        <v>39.33477785962962</v>
+        <v>39.00225308147471</v>
       </c>
       <c r="E86">
-        <v>106.176</v>
+        <v>107.44</v>
       </c>
       <c r="F86">
-        <v>106.176</v>
+        <v>107.44</v>
       </c>
       <c r="G86">
         <v>3.55</v>
@@ -8339,37 +8339,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M86">
-        <v>25.0363008</v>
+        <v>25.334352</v>
       </c>
       <c r="N86">
-        <v>-15.5663008</v>
+        <v>-15.864352</v>
       </c>
       <c r="O86">
-        <v>-1.400967072</v>
+        <v>-1.42779168</v>
       </c>
       <c r="P86">
-        <v>-14.165333728</v>
+        <v>-14.43656032</v>
       </c>
       <c r="Q86">
-        <v>-12.435333728</v>
+        <v>-12.70656032</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3341479191728739</v>
+        <v>0.3533711137843988</v>
       </c>
       <c r="T86">
-        <v>4.195813565219121</v>
+        <v>4.475534469567062</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03404256910030414</v>
+        <v>0.03364206828735939</v>
       </c>
       <c r="W86">
-        <v>0.2277727622061483</v>
+        <v>0.2278672002978407</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3782507677811571</v>
+        <v>0.3738007587484377</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2466927873208244</v>
+        <v>0.2485927873208244</v>
       </c>
       <c r="C87">
-        <v>-64.88774691852529</v>
+        <v>-66.47869669052986</v>
       </c>
       <c r="D87">
-        <v>39.00225308147471</v>
+        <v>38.67530330947016</v>
       </c>
       <c r="E87">
-        <v>107.44</v>
+        <v>108.704</v>
       </c>
       <c r="F87">
-        <v>107.44</v>
+        <v>108.704</v>
       </c>
       <c r="G87">
         <v>3.55</v>
@@ -8421,37 +8421,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M87">
-        <v>25.334352</v>
+        <v>25.6324032</v>
       </c>
       <c r="N87">
-        <v>-15.864352</v>
+        <v>-16.1624032</v>
       </c>
       <c r="O87">
-        <v>-1.42779168</v>
+        <v>-1.454616288</v>
       </c>
       <c r="P87">
-        <v>-14.43656032</v>
+        <v>-14.707786912</v>
       </c>
       <c r="Q87">
-        <v>-12.70656032</v>
+        <v>-12.977786912</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3533711137843988</v>
+        <v>0.375340479054713</v>
       </c>
       <c r="T87">
-        <v>4.475534469567062</v>
+        <v>4.795215503107567</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03364206828735939</v>
+        <v>0.03325088144680869</v>
       </c>
       <c r="W87">
-        <v>0.2278672002978407</v>
+        <v>0.2279594421548425</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3738007587484377</v>
+        <v>0.3694542382978744</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2485927873208244</v>
+        <v>0.2504927873208244</v>
       </c>
       <c r="C88">
-        <v>-66.47869669052986</v>
+        <v>-68.06421049406018</v>
       </c>
       <c r="D88">
-        <v>38.67530330947016</v>
+        <v>38.35378950593984</v>
       </c>
       <c r="E88">
-        <v>108.704</v>
+        <v>109.968</v>
       </c>
       <c r="F88">
-        <v>108.704</v>
+        <v>109.968</v>
       </c>
       <c r="G88">
         <v>3.55</v>
@@ -8503,37 +8503,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M88">
-        <v>25.6324032</v>
+        <v>25.9304544</v>
       </c>
       <c r="N88">
-        <v>-16.1624032</v>
+        <v>-16.4604544</v>
       </c>
       <c r="O88">
-        <v>-1.454616288</v>
+        <v>-1.481440896</v>
       </c>
       <c r="P88">
-        <v>-14.707786912</v>
+        <v>-14.979013504</v>
       </c>
       <c r="Q88">
-        <v>-12.977786912</v>
+        <v>-13.249013504</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.375340479054713</v>
+        <v>0.4006897466743063</v>
       </c>
       <c r="T88">
-        <v>4.795215503107567</v>
+        <v>5.164078234115841</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03325088144680869</v>
+        <v>0.03286868740719021</v>
       </c>
       <c r="W88">
-        <v>0.2279594421548425</v>
+        <v>0.2280495635093846</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3694542382978744</v>
+        <v>0.365207637857669</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2504927873208244</v>
+        <v>0.2523927873208244</v>
       </c>
       <c r="C89">
-        <v>-68.06421049406018</v>
+        <v>-69.6444227815431</v>
       </c>
       <c r="D89">
-        <v>38.35378950593984</v>
+        <v>38.0375772184569</v>
       </c>
       <c r="E89">
-        <v>109.968</v>
+        <v>111.232</v>
       </c>
       <c r="F89">
-        <v>109.968</v>
+        <v>111.232</v>
       </c>
       <c r="G89">
         <v>3.55</v>
@@ -8585,37 +8585,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M89">
-        <v>25.9304544</v>
+        <v>26.2285056</v>
       </c>
       <c r="N89">
-        <v>-16.4604544</v>
+        <v>-16.7585056</v>
       </c>
       <c r="O89">
-        <v>-1.481440896</v>
+        <v>-1.508265504</v>
       </c>
       <c r="P89">
-        <v>-14.979013504</v>
+        <v>-15.250240096</v>
       </c>
       <c r="Q89">
-        <v>-13.249013504</v>
+        <v>-13.520240096</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4006897466743063</v>
+        <v>0.4302638922304987</v>
       </c>
       <c r="T89">
-        <v>5.164078234115841</v>
+        <v>5.59441808695883</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03286868740719021</v>
+        <v>0.03249517959574486</v>
       </c>
       <c r="W89">
-        <v>0.2280495635093846</v>
+        <v>0.2281376366513234</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.365207637857669</v>
+        <v>0.3610575510638317</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2523927873208244</v>
+        <v>0.2542927873208244</v>
       </c>
       <c r="C90">
-        <v>-69.6444227815431</v>
+        <v>-71.21946360762871</v>
       </c>
       <c r="D90">
-        <v>38.0375772184569</v>
+        <v>37.7265363923713</v>
       </c>
       <c r="E90">
-        <v>111.232</v>
+        <v>112.496</v>
       </c>
       <c r="F90">
-        <v>111.232</v>
+        <v>112.496</v>
       </c>
       <c r="G90">
         <v>3.55</v>
@@ -8667,37 +8667,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M90">
-        <v>26.2285056</v>
+        <v>26.5265568</v>
       </c>
       <c r="N90">
-        <v>-16.7585056</v>
+        <v>-17.0565568</v>
       </c>
       <c r="O90">
-        <v>-1.508265504</v>
+        <v>-1.535090112</v>
       </c>
       <c r="P90">
-        <v>-15.250240096</v>
+        <v>-15.521466688</v>
       </c>
       <c r="Q90">
-        <v>-13.520240096</v>
+        <v>-13.791466688</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4302638922304987</v>
+        <v>0.4652151551605439</v>
       </c>
       <c r="T90">
-        <v>5.59441808695883</v>
+        <v>6.103001549409631</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03249517959574486</v>
+        <v>0.03213006521826458</v>
       </c>
       <c r="W90">
-        <v>0.2281376366513234</v>
+        <v>0.2282237306215332</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3610575510638317</v>
+        <v>0.3570007246473843</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2542927873208244</v>
+        <v>0.2561927873208244</v>
       </c>
       <c r="C91">
-        <v>-71.21946360762871</v>
+        <v>-72.78945880753922</v>
       </c>
       <c r="D91">
-        <v>37.7265363923713</v>
+        <v>37.42054119246079</v>
       </c>
       <c r="E91">
-        <v>112.496</v>
+        <v>113.76</v>
       </c>
       <c r="F91">
-        <v>112.496</v>
+        <v>113.76</v>
       </c>
       <c r="G91">
         <v>3.55</v>
@@ -8749,37 +8749,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M91">
-        <v>26.5265568</v>
+        <v>26.824608</v>
       </c>
       <c r="N91">
-        <v>-17.0565568</v>
+        <v>-17.354608</v>
       </c>
       <c r="O91">
-        <v>-1.535090112</v>
+        <v>-1.56191472</v>
       </c>
       <c r="P91">
-        <v>-15.521466688</v>
+        <v>-15.79269328</v>
       </c>
       <c r="Q91">
-        <v>-13.791466688</v>
+        <v>-14.06269328</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4652151551605439</v>
+        <v>0.5071566706765984</v>
       </c>
       <c r="T91">
-        <v>6.103001549409631</v>
+        <v>6.713301704350596</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03213006521826458</v>
+        <v>0.0317730644936172</v>
       </c>
       <c r="W91">
-        <v>0.2282237306215332</v>
+        <v>0.2283079113924051</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3570007246473843</v>
+        <v>0.3530340499290799</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2561927873208244</v>
+        <v>0.2580927873208244</v>
       </c>
       <c r="C92">
-        <v>-72.78945880753922</v>
+        <v>-74.35453016680866</v>
       </c>
       <c r="D92">
-        <v>37.42054119246079</v>
+        <v>37.11946983319136</v>
       </c>
       <c r="E92">
-        <v>113.76</v>
+        <v>115.024</v>
       </c>
       <c r="F92">
-        <v>113.76</v>
+        <v>115.024</v>
       </c>
       <c r="G92">
         <v>3.55</v>
@@ -8831,37 +8831,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M92">
-        <v>26.824608</v>
+        <v>27.1226592</v>
       </c>
       <c r="N92">
-        <v>-17.354608</v>
+        <v>-17.65265920000001</v>
       </c>
       <c r="O92">
-        <v>-1.56191472</v>
+        <v>-1.588739328</v>
       </c>
       <c r="P92">
-        <v>-15.79269328</v>
+        <v>-16.06391987200001</v>
       </c>
       <c r="Q92">
-        <v>-14.06269328</v>
+        <v>-14.33391987200001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5071566706765984</v>
+        <v>0.5584185229739982</v>
       </c>
       <c r="T92">
-        <v>6.713301704350596</v>
+        <v>7.459224115945107</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0317730644936172</v>
+        <v>0.03142390993874228</v>
       </c>
       <c r="W92">
-        <v>0.2283079113924051</v>
+        <v>0.2283902420364446</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3530340499290799</v>
+        <v>0.3491545548749142</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2580927873208244</v>
+        <v>0.2599927873208244</v>
       </c>
       <c r="C93">
-        <v>-74.35453016680866</v>
+        <v>-75.91479558289379</v>
       </c>
       <c r="D93">
-        <v>37.11946983319136</v>
+        <v>36.82320441710623</v>
       </c>
       <c r="E93">
-        <v>115.024</v>
+        <v>116.288</v>
       </c>
       <c r="F93">
-        <v>115.024</v>
+        <v>116.288</v>
       </c>
       <c r="G93">
         <v>3.55</v>
@@ -8913,37 +8913,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M93">
-        <v>27.1226592</v>
+        <v>27.4207104</v>
       </c>
       <c r="N93">
-        <v>-17.65265920000001</v>
+        <v>-17.95071040000001</v>
       </c>
       <c r="O93">
-        <v>-1.588739328</v>
+        <v>-1.615563936</v>
       </c>
       <c r="P93">
-        <v>-16.06391987200001</v>
+        <v>-16.335146464</v>
       </c>
       <c r="Q93">
-        <v>-14.33391987200001</v>
+        <v>-14.605146464</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5584185229739982</v>
+        <v>0.6224958383457482</v>
       </c>
       <c r="T93">
-        <v>7.459224115945107</v>
+        <v>8.391627130438248</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03142390993874228</v>
+        <v>0.03108234570027769</v>
       </c>
       <c r="W93">
-        <v>0.2283902420364446</v>
+        <v>0.2284707828838745</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3491545548749142</v>
+        <v>0.3453593966697521</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2599927873208244</v>
+        <v>0.2618927873208244</v>
       </c>
       <c r="C94">
-        <v>-75.91479558289379</v>
+        <v>-77.47036921910696</v>
       </c>
       <c r="D94">
-        <v>36.82320441710623</v>
+        <v>36.53163078089305</v>
       </c>
       <c r="E94">
-        <v>116.288</v>
+        <v>117.552</v>
       </c>
       <c r="F94">
-        <v>116.288</v>
+        <v>117.552</v>
       </c>
       <c r="G94">
         <v>3.55</v>
@@ -8995,37 +8995,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M94">
-        <v>27.4207104</v>
+        <v>27.7187616</v>
       </c>
       <c r="N94">
-        <v>-17.95071040000001</v>
+        <v>-18.24876160000001</v>
       </c>
       <c r="O94">
-        <v>-1.615563936</v>
+        <v>-1.642388544</v>
       </c>
       <c r="P94">
-        <v>-16.335146464</v>
+        <v>-16.60637305600001</v>
       </c>
       <c r="Q94">
-        <v>-14.605146464</v>
+        <v>-14.87637305600001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6224958383457482</v>
+        <v>0.7048809581094265</v>
       </c>
       <c r="T94">
-        <v>8.391627130438248</v>
+        <v>9.590431006215141</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03108234570027769</v>
+        <v>0.03074812692930696</v>
       </c>
       <c r="W94">
-        <v>0.2284707828838745</v>
+        <v>0.2285495916700694</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3453593966697521</v>
+        <v>0.3416458547700774</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2618927873208244</v>
+        <v>0.2637927873208244</v>
       </c>
       <c r="C95">
-        <v>-77.47036921910696</v>
+        <v>-79.02136165129343</v>
       </c>
       <c r="D95">
-        <v>36.53163078089305</v>
+        <v>36.24463834870659</v>
       </c>
       <c r="E95">
-        <v>117.552</v>
+        <v>118.816</v>
       </c>
       <c r="F95">
-        <v>117.552</v>
+        <v>118.816</v>
       </c>
       <c r="G95">
         <v>3.55</v>
@@ -9077,37 +9077,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M95">
-        <v>27.7187616</v>
+        <v>28.0168128</v>
       </c>
       <c r="N95">
-        <v>-18.24876160000001</v>
+        <v>-18.5468128</v>
       </c>
       <c r="O95">
-        <v>-1.642388544</v>
+        <v>-1.669213152</v>
       </c>
       <c r="P95">
-        <v>-16.60637305600001</v>
+        <v>-16.877599648</v>
       </c>
       <c r="Q95">
-        <v>-14.87637305600001</v>
+        <v>-15.147599648</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7048809581094265</v>
+        <v>0.8147277844609978</v>
       </c>
       <c r="T95">
-        <v>9.590431006215141</v>
+        <v>11.18883617391767</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03074812692930696</v>
+        <v>0.03042101919601646</v>
       </c>
       <c r="W95">
-        <v>0.2285495916700694</v>
+        <v>0.2286267236735793</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3416458547700774</v>
+        <v>0.3380113244001829</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2637927873208244</v>
+        <v>0.2656927873208244</v>
       </c>
       <c r="C96">
-        <v>-79.02136165129343</v>
+        <v>-80.56788000764843</v>
       </c>
       <c r="D96">
-        <v>36.24463834870659</v>
+        <v>35.96211999235159</v>
       </c>
       <c r="E96">
-        <v>118.816</v>
+        <v>120.08</v>
       </c>
       <c r="F96">
-        <v>118.816</v>
+        <v>120.08</v>
       </c>
       <c r="G96">
         <v>3.55</v>
@@ -9159,37 +9159,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M96">
-        <v>28.0168128</v>
+        <v>28.314864</v>
       </c>
       <c r="N96">
-        <v>-18.5468128</v>
+        <v>-18.844864</v>
       </c>
       <c r="O96">
-        <v>-1.669213152</v>
+        <v>-1.69603776</v>
       </c>
       <c r="P96">
-        <v>-16.877599648</v>
+        <v>-17.14882624000001</v>
       </c>
       <c r="Q96">
-        <v>-15.147599648</v>
+        <v>-15.41882624</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8147277844609978</v>
+        <v>0.9685133413531978</v>
       </c>
       <c r="T96">
-        <v>11.18883617391767</v>
+        <v>13.42660340870121</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03042101919601646</v>
+        <v>0.03010079794132155</v>
       </c>
       <c r="W96">
-        <v>0.2286267236735793</v>
+        <v>0.2287022318454364</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3380113244001829</v>
+        <v>0.3344533104591284</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2656927873208244</v>
+        <v>0.2675927873208244</v>
       </c>
       <c r="C97">
-        <v>-80.56788000764843</v>
+        <v>-82.11002810204619</v>
       </c>
       <c r="D97">
-        <v>35.96211999235159</v>
+        <v>35.68397189795383</v>
       </c>
       <c r="E97">
-        <v>120.08</v>
+        <v>121.344</v>
       </c>
       <c r="F97">
-        <v>120.08</v>
+        <v>121.344</v>
       </c>
       <c r="G97">
         <v>3.55</v>
@@ -9241,37 +9241,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M97">
-        <v>28.314864</v>
+        <v>28.6129152</v>
       </c>
       <c r="N97">
-        <v>-18.844864</v>
+        <v>-19.1429152</v>
       </c>
       <c r="O97">
-        <v>-1.69603776</v>
+        <v>-1.722862368</v>
       </c>
       <c r="P97">
-        <v>-17.14882624000001</v>
+        <v>-17.420052832</v>
       </c>
       <c r="Q97">
-        <v>-15.41882624</v>
+        <v>-15.690052832</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9685133413531978</v>
+        <v>1.199191676691498</v>
       </c>
       <c r="T97">
-        <v>13.42660340870121</v>
+        <v>16.78325426087652</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03010079794132155</v>
+        <v>0.02978724796276612</v>
       </c>
       <c r="W97">
-        <v>0.2287022318454364</v>
+        <v>0.2287761669303797</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3344533104591284</v>
+        <v>0.3309694218085124</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2675927873208244</v>
+        <v>0.2694927873208244</v>
       </c>
       <c r="C98">
-        <v>-82.11002810204616</v>
+        <v>-83.64790656122864</v>
       </c>
       <c r="D98">
-        <v>35.68397189795385</v>
+        <v>35.41009343877136</v>
       </c>
       <c r="E98">
-        <v>121.344</v>
+        <v>122.608</v>
       </c>
       <c r="F98">
-        <v>121.344</v>
+        <v>122.608</v>
       </c>
       <c r="G98">
         <v>3.55</v>
@@ -9323,37 +9323,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M98">
-        <v>28.6129152</v>
+        <v>28.9109664</v>
       </c>
       <c r="N98">
-        <v>-19.1429152</v>
+        <v>-19.4409664</v>
       </c>
       <c r="O98">
-        <v>-1.722862368</v>
+        <v>-1.749686976</v>
       </c>
       <c r="P98">
-        <v>-17.420052832</v>
+        <v>-17.691279424</v>
       </c>
       <c r="Q98">
-        <v>-15.690052832</v>
+        <v>-15.961279424</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.199191676691495</v>
+        <v>1.583655568921993</v>
       </c>
       <c r="T98">
-        <v>16.78325426087647</v>
+        <v>22.3776723478353</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02978724796276613</v>
+        <v>0.02948016293222214</v>
       </c>
       <c r="W98">
-        <v>0.2287761669303797</v>
+        <v>0.228848577580582</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3309694218085125</v>
+        <v>0.3275573659135793</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2694927873208244</v>
+        <v>0.2713927873208244</v>
       </c>
       <c r="C99">
-        <v>-83.64790656122864</v>
+        <v>-85.18161294618203</v>
       </c>
       <c r="D99">
-        <v>35.41009343877136</v>
+        <v>35.14038705381797</v>
       </c>
       <c r="E99">
-        <v>122.608</v>
+        <v>123.872</v>
       </c>
       <c r="F99">
-        <v>122.608</v>
+        <v>123.872</v>
       </c>
       <c r="G99">
         <v>3.55</v>
@@ -9405,37 +9405,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M99">
-        <v>28.9109664</v>
+        <v>29.2090176</v>
       </c>
       <c r="N99">
-        <v>-19.4409664</v>
+        <v>-19.7390176</v>
       </c>
       <c r="O99">
-        <v>-1.749686976</v>
+        <v>-1.776511584</v>
       </c>
       <c r="P99">
-        <v>-17.691279424</v>
+        <v>-17.962506016</v>
       </c>
       <c r="Q99">
-        <v>-15.961279424</v>
+        <v>-16.232506016</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.583655568921993</v>
+        <v>2.352583353382989</v>
       </c>
       <c r="T99">
-        <v>22.3776723478353</v>
+        <v>33.56650852175294</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02948016293222214</v>
+        <v>0.02917934494311783</v>
       </c>
       <c r="W99">
-        <v>0.228848577580582</v>
+        <v>0.2289195104624128</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3275573659135793</v>
+        <v>0.3242149438124203</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2713927873208244</v>
+        <v>0.2732927873208244</v>
       </c>
       <c r="C100">
-        <v>-85.18161294618203</v>
+        <v>-86.71124186800816</v>
       </c>
       <c r="D100">
-        <v>35.14038705381797</v>
+        <v>34.87475813199186</v>
       </c>
       <c r="E100">
-        <v>123.872</v>
+        <v>125.136</v>
       </c>
       <c r="F100">
-        <v>123.872</v>
+        <v>125.136</v>
       </c>
       <c r="G100">
         <v>3.55</v>
@@ -9487,37 +9487,37 @@
         <v>9.469999999999999</v>
       </c>
       <c r="M100">
-        <v>29.2090176</v>
+        <v>29.5070688</v>
       </c>
       <c r="N100">
-        <v>-19.7390176</v>
+        <v>-20.0370688</v>
       </c>
       <c r="O100">
-        <v>-1.776511584</v>
+        <v>-1.803336192</v>
       </c>
       <c r="P100">
-        <v>-17.962506016</v>
+        <v>-18.233732608</v>
       </c>
       <c r="Q100">
-        <v>-16.232506016</v>
+        <v>-16.503732608</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.352583353382989</v>
+        <v>4.659366706765979</v>
       </c>
       <c r="T100">
-        <v>33.56650852175294</v>
+        <v>67.13301704350589</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02917934494311783</v>
+        <v>0.02888460408510654</v>
       </c>
       <c r="W100">
-        <v>0.2289195104624128</v>
+        <v>0.2289890103567319</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3242149438124203</v>
+        <v>0.3209400453900727</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2732927873208244</v>
-      </c>
-      <c r="C101">
-        <v>-86.71124186800816</v>
-      </c>
-      <c r="D101">
-        <v>34.87475813199186</v>
-      </c>
-      <c r="E101">
-        <v>125.136</v>
-      </c>
-      <c r="F101">
-        <v>125.136</v>
-      </c>
-      <c r="G101">
-        <v>3.55</v>
-      </c>
-      <c r="H101">
-        <v>126.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>11.2</v>
-      </c>
-      <c r="K101">
-        <v>1.73</v>
-      </c>
-      <c r="L101">
-        <v>9.469999999999999</v>
-      </c>
-      <c r="M101">
-        <v>29.5070688</v>
-      </c>
-      <c r="N101">
-        <v>-20.0370688</v>
-      </c>
-      <c r="O101">
-        <v>-1.803336192</v>
-      </c>
-      <c r="P101">
-        <v>-18.233732608</v>
-      </c>
-      <c r="Q101">
-        <v>-16.503732608</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.659366706765979</v>
-      </c>
-      <c r="T101">
-        <v>67.13301704350589</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02888460408510654</v>
-      </c>
-      <c r="W101">
-        <v>0.2289890103567319</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3209400453900727</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
